--- a/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_11_49.xlsx
+++ b/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_11_49.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6532335.412776705</v>
+        <v>6491994.153938632</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6767152.318645783</v>
+        <v>6767152.318645789</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6767152.318645783</v>
+        <v>6767152.318645789</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2916902.906517471</v>
+        <v>2916902.906517478</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2916902.906517471</v>
+        <v>2916902.906517478</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>34534887.4657956</v>
+        <v>34534887.46579558</v>
       </c>
     </row>
   </sheetData>
@@ -654,10 +654,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>481.9993129555745</v>
+        <v>81.99931295557451</v>
       </c>
       <c r="C2" t="n">
-        <v>49.47457824299391</v>
+        <v>449.4745782429939</v>
       </c>
       <c r="D2" t="n">
         <v>10.33915573984979</v>
@@ -669,46 +669,46 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G2" t="n">
-        <v>3.75737228701621</v>
+        <v>403.7573722870162</v>
       </c>
       <c r="H2" t="n">
-        <v>8.009658703527407</v>
+        <v>408.0096587035274</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>797.8013999999999</v>
+        <v>418.7382696589336</v>
       </c>
       <c r="K2" t="n">
-        <v>97.12488247690055</v>
+        <v>313.1545016101228</v>
       </c>
       <c r="L2" t="n">
-        <v>31.55202437320317</v>
+        <v>814</v>
       </c>
       <c r="M2" t="n">
         <v>297.9910820919849</v>
       </c>
       <c r="N2" t="n">
+        <v>194.5855355810472</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
         <v>814</v>
-      </c>
-      <c r="O2" t="n">
-        <v>814</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>370.9706110579117</v>
       </c>
       <c r="R2" t="n">
-        <v>250.8785988282945</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>494.8481678023229</v>
+        <v>188.4175591877379</v>
       </c>
       <c r="T2" t="n">
-        <v>186.6755817285639</v>
+        <v>586.6755817285639</v>
       </c>
       <c r="U2" t="n">
         <v>249.2212965486107</v>
@@ -717,13 +717,13 @@
         <v>229.8510241668239</v>
       </c>
       <c r="W2" t="n">
-        <v>481.0642685380673</v>
+        <v>238.3734759809475</v>
       </c>
       <c r="X2" t="n">
         <v>192.2818334606677</v>
       </c>
       <c r="Y2" t="n">
-        <v>511.3174326828064</v>
+        <v>111.3174326828064</v>
       </c>
     </row>
     <row r="3">
@@ -751,10 +751,10 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>284.646359292943</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -781,7 +781,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R3" t="n">
-        <v>147.2737972923793</v>
+        <v>282.6256835075528</v>
       </c>
       <c r="S3" t="n">
         <v>66.5639999646113</v>
@@ -796,7 +796,7 @@
         <v>14.51066719152016</v>
       </c>
       <c r="W3" t="n">
-        <v>432.3731429098285</v>
+        <v>32.37314290982852</v>
       </c>
       <c r="X3" t="n">
         <v>19.86273944538755</v>
@@ -851,7 +851,7 @@
         <v>171.1850752716849</v>
       </c>
       <c r="O4" t="n">
-        <v>240.445564079015</v>
+        <v>211.2354862247911</v>
       </c>
       <c r="P4" t="n">
         <v>287.4478973282775</v>
@@ -860,7 +860,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R4" t="n">
-        <v>297.3920501269224</v>
+        <v>326.6021279811511</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -897,16 +897,16 @@
         <v>49.47457824299391</v>
       </c>
       <c r="D5" t="n">
-        <v>10.33915573984979</v>
+        <v>410.3391557398498</v>
       </c>
       <c r="E5" t="n">
-        <v>4.363289606868648</v>
+        <v>404.3632896068686</v>
       </c>
       <c r="F5" t="n">
         <v>4.889628708011855</v>
       </c>
       <c r="G5" t="n">
-        <v>3.75737228701621</v>
+        <v>347.2456039897461</v>
       </c>
       <c r="H5" t="n">
         <v>408.0096587035274</v>
@@ -915,19 +915,19 @@
         <v>150.0811596826846</v>
       </c>
       <c r="J5" t="n">
-        <v>797.8014000000035</v>
+        <v>797.8013999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>97.12488247690055</v>
+        <v>128.6769068501037</v>
       </c>
       <c r="L5" t="n">
-        <v>650.9664887921555</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>297.9910820919849</v>
       </c>
       <c r="N5" t="n">
-        <v>194.5855355810472</v>
+        <v>814</v>
       </c>
       <c r="O5" t="n">
         <v>814</v>
@@ -951,16 +951,16 @@
         <v>249.2212965486107</v>
       </c>
       <c r="V5" t="n">
-        <v>573.3392558695538</v>
+        <v>229.8510241668239</v>
       </c>
       <c r="W5" t="n">
         <v>238.3734759809475</v>
       </c>
       <c r="X5" t="n">
-        <v>592.2818334606677</v>
+        <v>192.2818334606677</v>
       </c>
       <c r="Y5" t="n">
-        <v>511.3174326828064</v>
+        <v>111.3174326828064</v>
       </c>
     </row>
     <row r="6">
@@ -970,13 +970,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>384.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>112.0691552915769</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -1015,7 +1015,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R6" t="n">
         <v>147.2737972923793</v>
@@ -1027,7 +1027,7 @@
         <v>5.357765217513816</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2103597601867477</v>
+        <v>323.7568066076106</v>
       </c>
       <c r="V6" t="n">
         <v>14.51066719152016</v>
@@ -1082,7 +1082,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>114.9691617061042</v>
+        <v>120.6316114025499</v>
       </c>
       <c r="N7" t="n">
         <v>171.1850752716849</v>
@@ -1097,7 +1097,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R7" t="n">
-        <v>326.6021279811511</v>
+        <v>320.9396782847018</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>481.9993129555745</v>
+        <v>81.99931295557451</v>
       </c>
       <c r="C8" t="n">
         <v>49.47457824299391</v>
@@ -1140,13 +1140,13 @@
         <v>4.363289606868648</v>
       </c>
       <c r="F8" t="n">
-        <v>404.8896287080119</v>
+        <v>4.889628708011855</v>
       </c>
       <c r="G8" t="n">
         <v>403.7573722870162</v>
       </c>
       <c r="H8" t="n">
-        <v>408.0096587035274</v>
+        <v>250.7004512606472</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1155,37 +1155,37 @@
         <v>418.7382696589336</v>
       </c>
       <c r="K8" t="n">
-        <v>97.12488247690061</v>
+        <v>611.1455837021119</v>
       </c>
       <c r="L8" t="n">
         <v>814</v>
       </c>
       <c r="M8" t="n">
-        <v>297.9910820919849</v>
+        <v>814</v>
       </c>
       <c r="N8" t="n">
         <v>194.5855355810472</v>
       </c>
       <c r="O8" t="n">
-        <v>216.0296191332221</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>814</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>370.9706110579117</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S8" t="n">
-        <v>94.84816780232291</v>
+        <v>494.8481678023229</v>
       </c>
       <c r="T8" t="n">
-        <v>280.2449731139786</v>
+        <v>186.6755817285639</v>
       </c>
       <c r="U8" t="n">
-        <v>249.2212965486107</v>
+        <v>649.2212965486107</v>
       </c>
       <c r="V8" t="n">
         <v>229.8510241668239</v>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1252,7 +1252,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R9" t="n">
         <v>147.2737972923793</v>
@@ -1264,10 +1264,10 @@
         <v>5.357765217513816</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2103597601867477</v>
+        <v>400.2103597601867</v>
       </c>
       <c r="V9" t="n">
-        <v>414.5106671915202</v>
+        <v>14.51066719152016</v>
       </c>
       <c r="W9" t="n">
         <v>32.37314290982852</v>
@@ -1276,7 +1276,7 @@
         <v>19.86273944538755</v>
       </c>
       <c r="Y9" t="n">
-        <v>240.5992384920742</v>
+        <v>284.6463592929431</v>
       </c>
     </row>
     <row r="10">
@@ -1316,10 +1316,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>23.54762815777917</v>
       </c>
       <c r="M10" t="n">
-        <v>114.9691617060999</v>
+        <v>120.6316114025499</v>
       </c>
       <c r="N10" t="n">
         <v>171.1850752716849</v>
@@ -1334,7 +1334,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R10" t="n">
-        <v>326.6021279811511</v>
+        <v>297.3920501269264</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1383,7 +1383,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>183.0096587035274</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1413,10 +1413,10 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>25.87859882829446</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>28.66928095685488</v>
+        <v>157.8556537644281</v>
       </c>
       <c r="T11" t="n">
         <v>361.6755817285639</v>
@@ -1434,7 +1434,7 @@
         <v>367.2818334606677</v>
       </c>
       <c r="Y11" t="n">
-        <v>286.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1526,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>47.72524664804467</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>3.77112610161862</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1562,7 +1562,7 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>340.7767994885277</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -1571,7 +1571,7 @@
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>298.1954887808113</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -1586,7 +1586,7 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.372809838709685</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>149.4679917525283</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>198.4745782429939</v>
+        <v>37.04328258398289</v>
       </c>
       <c r="D14" t="n">
         <v>159.3391557398498</v>
@@ -1614,13 +1614,13 @@
         <v>153.3632896068686</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>153.8896287080119</v>
       </c>
       <c r="G14" t="n">
         <v>152.7573722870162</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>157.0096587035274</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1802,16 +1802,16 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>436.4478973282775</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>92.1326498274306</v>
       </c>
       <c r="R16" t="n">
-        <v>417.2070674528526</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>111.3734797028554</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -2006,7 +2006,7 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>1.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -2033,7 +2033,7 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>292.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2042,13 +2042,13 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>446.839266425598</v>
+        <v>338.6387678008247</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>447.6021279811511</v>
       </c>
       <c r="S19" t="n">
-        <v>45.23564924773552</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2082,7 +2082,7 @@
         <v>170.4745782429939</v>
       </c>
       <c r="D20" t="n">
-        <v>130.9085471252638</v>
+        <v>131.3391557398498</v>
       </c>
       <c r="E20" t="n">
         <v>125.3632896068686</v>
@@ -2136,7 +2136,7 @@
         <v>370.2212965486107</v>
       </c>
       <c r="V20" t="n">
-        <v>350.8510241668239</v>
+        <v>350.4204155522921</v>
       </c>
       <c r="W20" t="n">
         <v>359.3734759809475</v>
@@ -2276,16 +2276,16 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>408.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>369.327645604236</v>
+        <v>255.2652880979692</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>447.6021279811511</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>83.37347970285543</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2303,7 +2303,7 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>8.465352849462363</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2331,7 +2331,7 @@
         <v>124.7573722870162</v>
       </c>
       <c r="H23" t="n">
-        <v>128.5790500890098</v>
+        <v>129.0096587035274</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2376,7 +2376,7 @@
         <v>350.8510241668239</v>
       </c>
       <c r="W23" t="n">
-        <v>359.3734759809475</v>
+        <v>358.9428673663618</v>
       </c>
       <c r="X23" t="n">
         <v>313.2818334606677</v>
@@ -2471,13 +2471,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7.860320195417028</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>6.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -2504,25 +2504,25 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>241.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>361.445564079015</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>408.4478973282775</v>
       </c>
       <c r="Q25" t="n">
-        <v>446.839266425598</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>16.3474343746833</v>
       </c>
       <c r="S25" t="n">
-        <v>83.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -2556,16 +2556,16 @@
         <v>224.4745782429939</v>
       </c>
       <c r="D26" t="n">
-        <v>185.3391557398498</v>
+        <v>43.17903827095238</v>
       </c>
       <c r="E26" t="n">
-        <v>179.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>178.7573722870162</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -2610,7 +2610,7 @@
         <v>424.2212965486107</v>
       </c>
       <c r="V26" t="n">
-        <v>262.084989378074</v>
+        <v>404.8510241668239</v>
       </c>
       <c r="W26" t="n">
         <v>413.3734759809475</v>
@@ -2720,7 +2720,7 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>49.38285596774193</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -2747,7 +2747,7 @@
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>292.7667533594955</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -2756,7 +2756,7 @@
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>340.7767994885277</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -2771,7 +2771,7 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.372809838709685</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
@@ -2796,16 +2796,16 @@
         <v>185.3391557398498</v>
       </c>
       <c r="E29" t="n">
-        <v>179.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>179.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>178.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>183.0096587035274</v>
+        <v>36.59725481811878</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2835,10 +2835,10 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>16.15509631013578</v>
+        <v>25.87859882829446</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>269.8481678023229</v>
       </c>
       <c r="T29" t="n">
         <v>361.6755817285639</v>
@@ -2847,7 +2847,7 @@
         <v>424.2212965486107</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>404.8510241668239</v>
       </c>
       <c r="W29" t="n">
         <v>413.3734759809475</v>
@@ -2960,7 +2960,7 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>20.04387284153003</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
         <v>3.77112610161862</v>
@@ -2972,7 +2972,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>63.52077380114304</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -2987,13 +2987,13 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>340.7767994885277</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>194.7467999963923</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -3014,7 +3014,7 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>62.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -3045,31 +3045,31 @@
         <v>117.0096587035274</v>
       </c>
       <c r="I32" t="n">
-        <v>8.45659138541424</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>377.7382696589756</v>
+        <v>377.7382696589747</v>
       </c>
       <c r="K32" t="n">
-        <v>727.107932076301</v>
+        <v>10.23281455297308</v>
       </c>
       <c r="L32" t="n">
-        <v>551.2932893429299</v>
+        <v>67.52171792390345</v>
       </c>
       <c r="M32" t="n">
-        <v>256.9910820920268</v>
+        <v>256.9910820920259</v>
       </c>
       <c r="N32" t="n">
-        <v>773.0000000000421</v>
+        <v>773.0000000000412</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>773.0000000000412</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>329.9706110579538</v>
+        <v>757.61730000004</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -3093,7 +3093,7 @@
         <v>301.2818334606677</v>
       </c>
       <c r="Y32" t="n">
-        <v>220.3174326828064</v>
+        <v>228.7740240682207</v>
       </c>
     </row>
     <row r="33">
@@ -3212,25 +3212,25 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>132.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>229.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>349.445564079015</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>70.05053078764654</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>434.839266425598</v>
       </c>
       <c r="R34" t="n">
-        <v>228.8671215550752</v>
+        <v>435.6021279811511</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -3282,31 +3282,31 @@
         <v>117.0096587035274</v>
       </c>
       <c r="I35" t="n">
-        <v>8.45659138541424</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>377.7382696589829</v>
+        <v>757.6173000000474</v>
       </c>
       <c r="K35" t="n">
-        <v>10.23281455323064</v>
+        <v>697.2557842276957</v>
       </c>
       <c r="L35" t="n">
         <v>773</v>
       </c>
       <c r="M35" t="n">
-        <v>256.991082092034</v>
+        <v>304.6719533611815</v>
       </c>
       <c r="N35" t="n">
-        <v>773.0000000000493</v>
+        <v>153.5855355810957</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>495.1684068660432</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>329.970611057961</v>
+        <v>329.9706110579601</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -3330,7 +3330,7 @@
         <v>301.2818334606677</v>
       </c>
       <c r="Y35" t="n">
-        <v>220.3174326828064</v>
+        <v>228.7740240682207</v>
       </c>
     </row>
     <row r="36">
@@ -3449,16 +3449,16 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>132.5476281577792</v>
       </c>
       <c r="M37" t="n">
         <v>229.6316114025499</v>
       </c>
       <c r="N37" t="n">
-        <v>275.2581858107181</v>
+        <v>280.1850752716849</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>298.1276103623819</v>
       </c>
       <c r="P37" t="n">
         <v>0</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>435.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -3513,7 +3513,7 @@
         <v>113.8896287080119</v>
       </c>
       <c r="G38" t="n">
-        <v>121.2139636724305</v>
+        <v>112.7573722870162</v>
       </c>
       <c r="H38" t="n">
         <v>117.0096587035274</v>
@@ -3522,34 +3522,34 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>377.7382696589902</v>
+        <v>377.7382696589893</v>
       </c>
       <c r="K38" t="n">
         <v>773</v>
       </c>
       <c r="L38" t="n">
-        <v>77.75453247715427</v>
+        <v>351.8156858378441</v>
       </c>
       <c r="M38" t="n">
-        <v>256.9910820920413</v>
+        <v>256.9910820920404</v>
       </c>
       <c r="N38" t="n">
-        <v>773.0000000000566</v>
+        <v>153.5855355811029</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>773.0000000000557</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>757.6173000000553</v>
+        <v>329.9706110579674</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>203.8481678023229</v>
+        <v>212.3047591877378</v>
       </c>
       <c r="T38" t="n">
         <v>295.6755817285639</v>
@@ -3689,22 +3689,22 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>225.4675834971399</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>280.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>70.05053078764654</v>
       </c>
       <c r="Q40" t="n">
         <v>434.839266425598</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>435.6021279811511</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>268.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>236.4745782429939</v>
       </c>
       <c r="D41" t="n">
         <v>197.3391557398498</v>
@@ -3750,10 +3750,10 @@
         <v>191.8896287080119</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>190.7573722870162</v>
       </c>
       <c r="H41" t="n">
-        <v>195.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3783,16 +3783,16 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>37.87859882829446</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>23.8794074380636</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>373.6755817285639</v>
+        <v>334.3067452582096</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>436.2212965486107</v>
       </c>
       <c r="V41" t="n">
         <v>416.8510241668239</v>
@@ -3804,7 +3804,7 @@
         <v>379.2818334606677</v>
       </c>
       <c r="Y41" t="n">
-        <v>298.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -3862,10 +3862,10 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>237.1775400585366</v>
+        <v>334.2737972923793</v>
       </c>
       <c r="S42" t="n">
-        <v>253.5639999646113</v>
+        <v>97.95951599123661</v>
       </c>
       <c r="T42" t="n">
         <v>192.3577652175138</v>
@@ -3883,7 +3883,7 @@
         <v>206.8627394453875</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>186.3913927661343</v>
       </c>
     </row>
     <row r="43">
@@ -3908,7 +3908,7 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>32.04387284153003</v>
       </c>
       <c r="H43" t="n">
         <v>15.77112610161862</v>
@@ -3932,7 +3932,7 @@
         <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>257.9707994885276</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
         <v>0</v>
@@ -3972,16 +3972,16 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>294.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>262.4745782429939</v>
+        <v>104.3195395389828</v>
       </c>
       <c r="D44" t="n">
-        <v>25.52655804696926</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>217.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -4020,10 +4020,10 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>63.87859882829446</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>307.8481678023229</v>
       </c>
       <c r="T44" t="n">
         <v>0</v>
@@ -4041,7 +4041,7 @@
         <v>405.2818334606677</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>324.3174326828064</v>
       </c>
     </row>
     <row r="45">
@@ -4051,13 +4051,13 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>196.5851473477758</v>
+        <v>197.5565566463266</v>
       </c>
       <c r="C45" t="n">
         <v>174.0999124455193</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>160.9376868977026</v>
       </c>
       <c r="E45" t="n">
         <v>155.6720972219126</v>
@@ -4069,7 +4069,7 @@
         <v>138.7395358750273</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>145.1680871864211</v>
       </c>
       <c r="I45" t="n">
         <v>30.12638589134853</v>
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>279.5639999646113</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
         <v>218.3577652175138</v>
@@ -4114,7 +4114,7 @@
         <v>227.5106671915202</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>16.55705513387049</v>
       </c>
       <c r="X45" t="n">
         <v>232.8627394453875</v>
@@ -4148,7 +4148,7 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>41.77112610161862</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
@@ -4169,7 +4169,7 @@
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>159.0013573820787</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
         <v>12.17031021621619</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>39.37280983870968</v>
       </c>
       <c r="X46" t="n">
         <v>0</v>
@@ -4297,22 +4297,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>146.7701851396645</v>
+        <v>1358.891397260877</v>
       </c>
       <c r="C2" t="n">
-        <v>96.79586368209488</v>
+        <v>904.876671762903</v>
       </c>
       <c r="D2" t="n">
-        <v>86.35227202568095</v>
+        <v>894.4330801064891</v>
       </c>
       <c r="E2" t="n">
-        <v>81.94490878641969</v>
+        <v>890.0257168672279</v>
       </c>
       <c r="F2" t="n">
-        <v>77.00588988943801</v>
+        <v>885.0866979702462</v>
       </c>
       <c r="G2" t="n">
-        <v>73.21056434699739</v>
+        <v>477.2509683874014</v>
       </c>
       <c r="H2" t="n">
         <v>65.12</v>
@@ -4321,22 +4321,22 @@
         <v>65.12</v>
       </c>
       <c r="J2" t="n">
-        <v>65.12</v>
+        <v>448.0120508495621</v>
       </c>
       <c r="K2" t="n">
-        <v>772.8740581041409</v>
+        <v>937.5543724554985</v>
       </c>
       <c r="L2" t="n">
-        <v>1546.863326414037</v>
+        <v>921.1921502332762</v>
       </c>
       <c r="M2" t="n">
-        <v>2051.72223339183</v>
+        <v>1426.051057211069</v>
       </c>
       <c r="N2" t="n">
-        <v>2035.360011169608</v>
+        <v>2035.360011169607</v>
       </c>
       <c r="O2" t="n">
-        <v>2018.997788947385</v>
+        <v>2841.220011169607</v>
       </c>
       <c r="P2" t="n">
         <v>2824.857788947385</v>
@@ -4345,28 +4345,28 @@
         <v>3256</v>
       </c>
       <c r="R2" t="n">
-        <v>3002.587273910814</v>
+        <v>3256</v>
       </c>
       <c r="S2" t="n">
-        <v>2502.740639767053</v>
+        <v>3065.679233143699</v>
       </c>
       <c r="T2" t="n">
-        <v>2314.179446101837</v>
+        <v>2473.077635438079</v>
       </c>
       <c r="U2" t="n">
-        <v>2062.440762719402</v>
+        <v>2221.338952055644</v>
       </c>
       <c r="V2" t="n">
-        <v>1830.268011035741</v>
+        <v>1989.166200371984</v>
       </c>
       <c r="W2" t="n">
-        <v>1344.344507461936</v>
+        <v>1748.38491150234</v>
       </c>
       <c r="X2" t="n">
-        <v>1150.120433259241</v>
+        <v>1554.160837299645</v>
       </c>
       <c r="Y2" t="n">
-        <v>633.6381780240832</v>
+        <v>1441.718986104891</v>
       </c>
     </row>
     <row r="3">
@@ -4376,76 +4376,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2388.089154674841</v>
+        <v>619.9629020987572</v>
       </c>
       <c r="C3" t="n">
-        <v>2388.089154674841</v>
+        <v>619.9629020987572</v>
       </c>
       <c r="D3" t="n">
-        <v>2388.089154674841</v>
+        <v>619.9629020987572</v>
       </c>
       <c r="E3" t="n">
-        <v>2388.089154674841</v>
+        <v>619.9629020987572</v>
       </c>
       <c r="F3" t="n">
-        <v>2388.089154674841</v>
+        <v>619.9629020987572</v>
       </c>
       <c r="G3" t="n">
-        <v>2388.089154674841</v>
+        <v>619.9629020987572</v>
       </c>
       <c r="H3" t="n">
-        <v>2100.567579631464</v>
+        <v>284.4395817084329</v>
       </c>
       <c r="I3" t="n">
-        <v>2100.567579631464</v>
+        <v>65.12</v>
       </c>
       <c r="J3" t="n">
-        <v>2224.524099806763</v>
+        <v>189.076520175299</v>
       </c>
       <c r="K3" t="n">
-        <v>2413.716915901147</v>
+        <v>378.2693362696824</v>
       </c>
       <c r="L3" t="n">
-        <v>2685.067377496347</v>
+        <v>649.6197978648825</v>
       </c>
       <c r="M3" t="n">
-        <v>2771.147919239206</v>
+        <v>735.7003396077417</v>
       </c>
       <c r="N3" t="n">
-        <v>2904.428203846775</v>
+        <v>868.9806242153101</v>
       </c>
       <c r="O3" t="n">
-        <v>3143.470655530493</v>
+        <v>1108.023075899029</v>
       </c>
       <c r="P3" t="n">
-        <v>3256</v>
+        <v>1220.552420368536</v>
       </c>
       <c r="Q3" t="n">
-        <v>3081.172459504566</v>
+        <v>1045.724879873102</v>
       </c>
       <c r="R3" t="n">
-        <v>2932.411048098123</v>
+        <v>760.2443914816341</v>
       </c>
       <c r="S3" t="n">
-        <v>2865.174684497505</v>
+        <v>693.0080278810167</v>
       </c>
       <c r="T3" t="n">
-        <v>2859.76280043941</v>
+        <v>687.5961438229219</v>
       </c>
       <c r="U3" t="n">
-        <v>2859.550315833161</v>
+        <v>687.3836592166726</v>
       </c>
       <c r="V3" t="n">
-        <v>2844.893076245767</v>
+        <v>672.7264196292786</v>
       </c>
       <c r="W3" t="n">
-        <v>2408.152527852</v>
+        <v>640.0262752759164</v>
       </c>
       <c r="X3" t="n">
-        <v>2388.089154674841</v>
+        <v>619.9629020987572</v>
       </c>
       <c r="Y3" t="n">
-        <v>2388.089154674841</v>
+        <v>619.9629020987572</v>
       </c>
     </row>
     <row r="4">
@@ -4455,76 +4455,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>923.5983371018272</v>
+        <v>698.5682646830375</v>
       </c>
       <c r="C4" t="n">
-        <v>1049.600342920263</v>
+        <v>698.5682646830375</v>
       </c>
       <c r="D4" t="n">
-        <v>1162.919487045263</v>
+        <v>698.5682646830375</v>
       </c>
       <c r="E4" t="n">
-        <v>1162.919487045263</v>
+        <v>698.5682646830375</v>
       </c>
       <c r="F4" t="n">
-        <v>1287.280459637198</v>
+        <v>698.5682646830375</v>
       </c>
       <c r="G4" t="n">
-        <v>1440.687025524084</v>
+        <v>698.5682646830375</v>
       </c>
       <c r="H4" t="n">
-        <v>1440.687025524084</v>
+        <v>853.8410604057406</v>
       </c>
       <c r="I4" t="n">
-        <v>1440.687025524084</v>
+        <v>1074.973939341824</v>
       </c>
       <c r="J4" t="n">
-        <v>1440.687025524084</v>
+        <v>1436.057679994275</v>
       </c>
       <c r="K4" t="n">
-        <v>1546.422113931138</v>
+        <v>1546.422113931143</v>
       </c>
       <c r="L4" t="n">
-        <v>1522.636630943483</v>
+        <v>1522.636630943487</v>
       </c>
       <c r="M4" t="n">
-        <v>1400.786518415654</v>
+        <v>1400.786518415659</v>
       </c>
       <c r="N4" t="n">
-        <v>1227.872300969508</v>
+        <v>1227.872300969513</v>
       </c>
       <c r="O4" t="n">
-        <v>984.9979938189878</v>
+        <v>1014.503122964673</v>
       </c>
       <c r="P4" t="n">
-        <v>694.6465823762833</v>
+        <v>724.1517115219688</v>
       </c>
       <c r="Q4" t="n">
-        <v>365.5160102292145</v>
+        <v>395.0211393749001</v>
       </c>
       <c r="R4" t="n">
         <v>65.12</v>
       </c>
       <c r="S4" t="n">
-        <v>102.3702550941731</v>
+        <v>65.12</v>
       </c>
       <c r="T4" t="n">
-        <v>290.445934252978</v>
+        <v>253.1956791588049</v>
       </c>
       <c r="U4" t="n">
-        <v>290.445934252978</v>
+        <v>499.7468717970915</v>
       </c>
       <c r="V4" t="n">
-        <v>489.2673271389239</v>
+        <v>698.5682646830375</v>
       </c>
       <c r="W4" t="n">
-        <v>661.1582453986014</v>
+        <v>698.5682646830375</v>
       </c>
       <c r="X4" t="n">
-        <v>812.1890364227949</v>
+        <v>698.5682646830375</v>
       </c>
       <c r="Y4" t="n">
-        <v>923.5983371018272</v>
+        <v>698.5682646830375</v>
       </c>
     </row>
     <row r="5">
@@ -4534,19 +4534,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>702.4077201726793</v>
+        <v>1857.446338054225</v>
       </c>
       <c r="C5" t="n">
-        <v>652.4333987151097</v>
+        <v>1807.472016596655</v>
       </c>
       <c r="D5" t="n">
-        <v>641.9898070586958</v>
+        <v>1392.988020899837</v>
       </c>
       <c r="E5" t="n">
-        <v>637.5824438194345</v>
+        <v>984.5402536201717</v>
       </c>
       <c r="F5" t="n">
-        <v>632.6434249224528</v>
+        <v>979.60123472319</v>
       </c>
       <c r="G5" t="n">
         <v>628.8480993800122</v>
@@ -4561,13 +4561,13 @@
         <v>65.12</v>
       </c>
       <c r="K5" t="n">
-        <v>772.8740581041409</v>
+        <v>741.0033264140367</v>
       </c>
       <c r="L5" t="n">
-        <v>921.1921502332766</v>
+        <v>1546.863326414037</v>
       </c>
       <c r="M5" t="n">
-        <v>1426.05105721107</v>
+        <v>2051.72223339183</v>
       </c>
       <c r="N5" t="n">
         <v>2035.360011169608</v>
@@ -4594,16 +4594,16 @@
         <v>2719.893892848992</v>
       </c>
       <c r="V5" t="n">
-        <v>2140.763331364595</v>
+        <v>2487.721141165332</v>
       </c>
       <c r="W5" t="n">
-        <v>1899.982042494951</v>
+        <v>2246.939852295688</v>
       </c>
       <c r="X5" t="n">
-        <v>1301.717564251852</v>
+        <v>2052.715778092993</v>
       </c>
       <c r="Y5" t="n">
-        <v>785.2353090166939</v>
+        <v>1940.273926898239</v>
       </c>
     </row>
     <row r="6">
@@ -4613,10 +4613,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>543.0685532697942</v>
+        <v>429.8673863086054</v>
       </c>
       <c r="C6" t="n">
-        <v>178.3211669611888</v>
+        <v>65.12</v>
       </c>
       <c r="D6" t="n">
         <v>65.12</v>
@@ -4658,31 +4658,31 @@
         <v>1220.552420368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1220.552420368536</v>
+        <v>1045.724879873102</v>
       </c>
       <c r="R6" t="n">
-        <v>1071.791008962092</v>
+        <v>896.9634684666578</v>
       </c>
       <c r="S6" t="n">
-        <v>1004.554645361474</v>
+        <v>829.7271048660403</v>
       </c>
       <c r="T6" t="n">
-        <v>999.1427613033796</v>
+        <v>824.3152208079456</v>
       </c>
       <c r="U6" t="n">
-        <v>998.9302766971304</v>
+        <v>497.2881434265207</v>
       </c>
       <c r="V6" t="n">
-        <v>984.2730371097363</v>
+        <v>482.6309038391266</v>
       </c>
       <c r="W6" t="n">
-        <v>951.5728927563741</v>
+        <v>449.9307594857645</v>
       </c>
       <c r="X6" t="n">
-        <v>931.509519579215</v>
+        <v>429.8673863086054</v>
       </c>
       <c r="Y6" t="n">
-        <v>931.509519579215</v>
+        <v>429.8673863086054</v>
       </c>
     </row>
     <row r="7">
@@ -4692,52 +4692,52 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>660.3127671909447</v>
+        <v>648.1707399820555</v>
       </c>
       <c r="C7" t="n">
-        <v>660.3127671909447</v>
+        <v>774.1727458004913</v>
       </c>
       <c r="D7" t="n">
-        <v>773.6319113159448</v>
+        <v>774.1727458004913</v>
       </c>
       <c r="E7" t="n">
-        <v>891.4608155273578</v>
+        <v>892.0016500119043</v>
       </c>
       <c r="F7" t="n">
-        <v>1015.821788119293</v>
+        <v>892.0016500119043</v>
       </c>
       <c r="G7" t="n">
-        <v>1015.821788119293</v>
+        <v>1045.40821589879</v>
       </c>
       <c r="H7" t="n">
-        <v>1185.338373278691</v>
+        <v>1214.924801058187</v>
       </c>
       <c r="I7" t="n">
-        <v>1185.338373278691</v>
+        <v>1436.05767999427</v>
       </c>
       <c r="J7" t="n">
-        <v>1546.422113931142</v>
+        <v>1436.05767999427</v>
       </c>
       <c r="K7" t="n">
-        <v>1546.422113931142</v>
+        <v>1546.422113931139</v>
       </c>
       <c r="L7" t="n">
-        <v>1546.422113931142</v>
+        <v>1546.422113931139</v>
       </c>
       <c r="M7" t="n">
-        <v>1430.29164756134</v>
+        <v>1424.57200140331</v>
       </c>
       <c r="N7" t="n">
-        <v>1257.377430115193</v>
+        <v>1251.657783957164</v>
       </c>
       <c r="O7" t="n">
-        <v>1014.503122964673</v>
+        <v>1008.783476806644</v>
       </c>
       <c r="P7" t="n">
-        <v>724.1517115219688</v>
+        <v>718.4320653639393</v>
       </c>
       <c r="Q7" t="n">
-        <v>395.0211393749001</v>
+        <v>389.3014932168705</v>
       </c>
       <c r="R7" t="n">
         <v>65.12</v>
@@ -4746,22 +4746,22 @@
         <v>102.3702550941731</v>
       </c>
       <c r="T7" t="n">
-        <v>290.445934252978</v>
+        <v>117.9712914177993</v>
       </c>
       <c r="U7" t="n">
-        <v>290.445934252978</v>
+        <v>364.5224840560859</v>
       </c>
       <c r="V7" t="n">
-        <v>290.445934252978</v>
+        <v>364.5224840560859</v>
       </c>
       <c r="W7" t="n">
-        <v>397.5246385004589</v>
+        <v>536.4134023157633</v>
       </c>
       <c r="X7" t="n">
-        <v>548.5554295246525</v>
+        <v>536.4134023157633</v>
       </c>
       <c r="Y7" t="n">
-        <v>548.5554295246525</v>
+        <v>536.4134023157633</v>
       </c>
     </row>
     <row r="8">
@@ -4771,22 +4771,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1358.891397260877</v>
+        <v>795.95280388423</v>
       </c>
       <c r="C8" t="n">
-        <v>1308.917075803307</v>
+        <v>745.9784824266603</v>
       </c>
       <c r="D8" t="n">
-        <v>1298.473484146893</v>
+        <v>735.5348907702464</v>
       </c>
       <c r="E8" t="n">
-        <v>1294.066120907632</v>
+        <v>731.1275275309852</v>
       </c>
       <c r="F8" t="n">
-        <v>885.0866979702462</v>
+        <v>726.1885086340035</v>
       </c>
       <c r="G8" t="n">
-        <v>477.2509683874014</v>
+        <v>318.3527790511588</v>
       </c>
       <c r="H8" t="n">
         <v>65.12</v>
@@ -4798,19 +4798,19 @@
         <v>448.0120508495621</v>
       </c>
       <c r="K8" t="n">
-        <v>1155.766108953703</v>
+        <v>636.5532794332872</v>
       </c>
       <c r="L8" t="n">
-        <v>1139.40388673148</v>
+        <v>620.191057211065</v>
       </c>
       <c r="M8" t="n">
-        <v>1644.262793709273</v>
+        <v>603.8288349888427</v>
       </c>
       <c r="N8" t="n">
-        <v>2253.571747667811</v>
+        <v>1213.137788947381</v>
       </c>
       <c r="O8" t="n">
-        <v>2841.220011169607</v>
+        <v>2018.997788947385</v>
       </c>
       <c r="P8" t="n">
         <v>2824.857788947385</v>
@@ -4819,28 +4819,28 @@
         <v>3256</v>
       </c>
       <c r="R8" t="n">
-        <v>3256</v>
+        <v>3002.587273910814</v>
       </c>
       <c r="S8" t="n">
-        <v>3160.193769896644</v>
+        <v>2502.740639767053</v>
       </c>
       <c r="T8" t="n">
-        <v>2877.118039478483</v>
+        <v>2314.179446101837</v>
       </c>
       <c r="U8" t="n">
-        <v>2625.379356096048</v>
+        <v>1658.400358678998</v>
       </c>
       <c r="V8" t="n">
-        <v>2393.206604412388</v>
+        <v>1426.227606995337</v>
       </c>
       <c r="W8" t="n">
-        <v>2152.425315542744</v>
+        <v>1185.446318125693</v>
       </c>
       <c r="X8" t="n">
-        <v>1958.20124134005</v>
+        <v>991.2222439229986</v>
       </c>
       <c r="Y8" t="n">
-        <v>1845.759390145296</v>
+        <v>878.7803927282447</v>
       </c>
     </row>
     <row r="9">
@@ -4850,25 +4850,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>284.4395817084329</v>
+        <v>65.12</v>
       </c>
       <c r="C9" t="n">
-        <v>284.4395817084329</v>
+        <v>65.12</v>
       </c>
       <c r="D9" t="n">
-        <v>284.4395817084329</v>
+        <v>65.12</v>
       </c>
       <c r="E9" t="n">
-        <v>284.4395817084329</v>
+        <v>65.12</v>
       </c>
       <c r="F9" t="n">
-        <v>284.4395817084329</v>
+        <v>65.12</v>
       </c>
       <c r="G9" t="n">
-        <v>284.4395817084329</v>
+        <v>65.12</v>
       </c>
       <c r="H9" t="n">
-        <v>284.4395817084329</v>
+        <v>65.12</v>
       </c>
       <c r="I9" t="n">
         <v>65.12</v>
@@ -4895,31 +4895,31 @@
         <v>1220.552420368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1220.552420368536</v>
+        <v>1045.724879873102</v>
       </c>
       <c r="R9" t="n">
-        <v>1071.791008962092</v>
+        <v>896.9634684666578</v>
       </c>
       <c r="S9" t="n">
-        <v>1004.554645361474</v>
+        <v>829.7271048660403</v>
       </c>
       <c r="T9" t="n">
-        <v>999.1427613033796</v>
+        <v>824.3152208079456</v>
       </c>
       <c r="U9" t="n">
-        <v>998.9302766971304</v>
+        <v>420.0623321612923</v>
       </c>
       <c r="V9" t="n">
-        <v>580.2326330693322</v>
+        <v>405.4050925738982</v>
       </c>
       <c r="W9" t="n">
-        <v>547.5324887159701</v>
+        <v>372.704948220536</v>
       </c>
       <c r="X9" t="n">
-        <v>527.4691155388109</v>
+        <v>352.6415750433769</v>
       </c>
       <c r="Y9" t="n">
-        <v>284.4395817084329</v>
+        <v>65.12</v>
       </c>
     </row>
     <row r="10">
@@ -4929,52 +4929,52 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>799.7852555817501</v>
+        <v>523.809767390124</v>
       </c>
       <c r="C10" t="n">
-        <v>925.7872614001859</v>
+        <v>649.8117732085598</v>
       </c>
       <c r="D10" t="n">
-        <v>1039.106405525186</v>
+        <v>649.8117732085598</v>
       </c>
       <c r="E10" t="n">
-        <v>1039.106405525186</v>
+        <v>767.6406774199728</v>
       </c>
       <c r="F10" t="n">
-        <v>1039.106405525186</v>
+        <v>892.0016500119083</v>
       </c>
       <c r="G10" t="n">
-        <v>1192.512971412071</v>
+        <v>1045.408215898794</v>
       </c>
       <c r="H10" t="n">
-        <v>1362.029556571469</v>
+        <v>1214.924801058191</v>
       </c>
       <c r="I10" t="n">
-        <v>1362.029556571469</v>
+        <v>1436.057679994274</v>
       </c>
       <c r="J10" t="n">
-        <v>1436.057679994269</v>
+        <v>1436.057679994274</v>
       </c>
       <c r="K10" t="n">
-        <v>1546.422113931138</v>
+        <v>1546.422113931143</v>
       </c>
       <c r="L10" t="n">
-        <v>1546.422113931138</v>
+        <v>1522.636630943487</v>
       </c>
       <c r="M10" t="n">
-        <v>1430.29164756134</v>
+        <v>1400.786518415659</v>
       </c>
       <c r="N10" t="n">
-        <v>1257.377430115193</v>
+        <v>1227.872300969512</v>
       </c>
       <c r="O10" t="n">
-        <v>1014.503122964673</v>
+        <v>984.9979938189919</v>
       </c>
       <c r="P10" t="n">
-        <v>724.1517115219688</v>
+        <v>694.6465823762874</v>
       </c>
       <c r="Q10" t="n">
-        <v>395.0211393749001</v>
+        <v>365.5160102292186</v>
       </c>
       <c r="R10" t="n">
         <v>65.12</v>
@@ -4983,22 +4983,22 @@
         <v>102.3702550941731</v>
       </c>
       <c r="T10" t="n">
-        <v>290.445934252978</v>
+        <v>102.3702550941731</v>
       </c>
       <c r="U10" t="n">
-        <v>536.9971268912645</v>
+        <v>102.3702550941731</v>
       </c>
       <c r="V10" t="n">
-        <v>536.9971268912645</v>
+        <v>240.1615114641544</v>
       </c>
       <c r="W10" t="n">
-        <v>536.9971268912645</v>
+        <v>412.0524297238318</v>
       </c>
       <c r="X10" t="n">
-        <v>688.027917915458</v>
+        <v>412.0524297238318</v>
       </c>
       <c r="Y10" t="n">
-        <v>688.027917915458</v>
+        <v>412.0524297238318</v>
       </c>
     </row>
     <row r="11">
@@ -5008,22 +5008,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>660.7799623139956</v>
+        <v>845.6382034286696</v>
       </c>
       <c r="C11" t="n">
-        <v>434.0379640887492</v>
+        <v>618.8962052034233</v>
       </c>
       <c r="D11" t="n">
-        <v>246.8266956646584</v>
+        <v>431.6849367793326</v>
       </c>
       <c r="E11" t="n">
-        <v>246.8266956646584</v>
+        <v>431.6849367793326</v>
       </c>
       <c r="F11" t="n">
-        <v>65.12</v>
+        <v>249.9782411146742</v>
       </c>
       <c r="G11" t="n">
-        <v>65.12</v>
+        <v>249.9782411146742</v>
       </c>
       <c r="H11" t="n">
         <v>65.12</v>
@@ -5032,52 +5032,52 @@
         <v>65.12</v>
       </c>
       <c r="J11" t="n">
-        <v>65.12</v>
+        <v>456.4291130376557</v>
       </c>
       <c r="K11" t="n">
-        <v>225.1996802252368</v>
+        <v>1166.135479385524</v>
       </c>
       <c r="L11" t="n">
-        <v>1031.059680225237</v>
+        <v>1166.135479385524</v>
       </c>
       <c r="M11" t="n">
-        <v>1031.059680225237</v>
+        <v>1676.984308114459</v>
       </c>
       <c r="N11" t="n">
-        <v>1644.28</v>
+        <v>2290.204627889222</v>
       </c>
       <c r="O11" t="n">
-        <v>2450.14</v>
+        <v>2817.400904947332</v>
       </c>
       <c r="P11" t="n">
-        <v>3256</v>
+        <v>2817.400904947332</v>
       </c>
       <c r="Q11" t="n">
         <v>3256</v>
       </c>
       <c r="R11" t="n">
-        <v>3229.860001183541</v>
+        <v>3256</v>
       </c>
       <c r="S11" t="n">
-        <v>3200.901131530152</v>
+        <v>3096.549844682396</v>
       </c>
       <c r="T11" t="n">
-        <v>2835.572261097259</v>
+        <v>2731.220974249503</v>
       </c>
       <c r="U11" t="n">
-        <v>2407.065900947147</v>
+        <v>2302.714614099391</v>
       </c>
       <c r="V11" t="n">
-        <v>1998.12547249581</v>
+        <v>1893.774185648053</v>
       </c>
       <c r="W11" t="n">
-        <v>1580.576506858489</v>
+        <v>1476.225220010733</v>
       </c>
       <c r="X11" t="n">
-        <v>1209.584755888118</v>
+        <v>1105.233469040361</v>
       </c>
       <c r="Y11" t="n">
-        <v>920.3752279256871</v>
+        <v>1105.233469040361</v>
       </c>
     </row>
     <row r="12">
@@ -5108,19 +5108,19 @@
         <v>65.12</v>
       </c>
       <c r="I12" t="n">
-        <v>65.12</v>
+        <v>72.91487796756496</v>
       </c>
       <c r="J12" t="n">
-        <v>411.826520175299</v>
+        <v>419.6213981428639</v>
       </c>
       <c r="K12" t="n">
-        <v>823.7693362696824</v>
+        <v>831.5642142372474</v>
       </c>
       <c r="L12" t="n">
-        <v>1121.840378378698</v>
+        <v>1325.664675832448</v>
       </c>
       <c r="M12" t="n">
-        <v>1430.670920121557</v>
+        <v>1634.495217575307</v>
       </c>
       <c r="N12" t="n">
         <v>1786.701204729125</v>
@@ -5166,52 +5166,52 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>178.8182646830375</v>
+        <v>177.4315880782802</v>
       </c>
       <c r="C13" t="n">
-        <v>130.6109448365277</v>
+        <v>177.4315880782802</v>
       </c>
       <c r="D13" t="n">
-        <v>130.6109448365277</v>
+        <v>177.4315880782802</v>
       </c>
       <c r="E13" t="n">
-        <v>130.6109448365277</v>
+        <v>177.4315880782802</v>
       </c>
       <c r="F13" t="n">
-        <v>130.6109448365277</v>
+        <v>177.4315880782802</v>
       </c>
       <c r="G13" t="n">
-        <v>130.6109448365277</v>
+        <v>177.4315880782802</v>
       </c>
       <c r="H13" t="n">
-        <v>130.6109448365277</v>
+        <v>173.6223697938169</v>
       </c>
       <c r="I13" t="n">
-        <v>178.4938237726106</v>
+        <v>221.5052487298998</v>
       </c>
       <c r="J13" t="n">
-        <v>366.3275644250619</v>
+        <v>409.3389893823512</v>
       </c>
       <c r="K13" t="n">
-        <v>366.3275644250619</v>
+        <v>409.3389893823512</v>
       </c>
       <c r="L13" t="n">
-        <v>366.3275644250619</v>
+        <v>409.3389893823512</v>
       </c>
       <c r="M13" t="n">
-        <v>366.3275644250619</v>
+        <v>409.3389893823512</v>
       </c>
       <c r="N13" t="n">
-        <v>366.3275644250619</v>
+        <v>409.3389893823512</v>
       </c>
       <c r="O13" t="n">
-        <v>366.3275644250619</v>
+        <v>65.12</v>
       </c>
       <c r="P13" t="n">
-        <v>366.3275644250619</v>
+        <v>65.12</v>
       </c>
       <c r="Q13" t="n">
-        <v>366.3275644250619</v>
+        <v>65.12</v>
       </c>
       <c r="R13" t="n">
         <v>65.12</v>
@@ -5229,13 +5229,13 @@
         <v>178.8182646830375</v>
       </c>
       <c r="W13" t="n">
-        <v>178.8182646830375</v>
+        <v>177.4315880782802</v>
       </c>
       <c r="X13" t="n">
-        <v>178.8182646830375</v>
+        <v>177.4315880782802</v>
       </c>
       <c r="Y13" t="n">
-        <v>178.8182646830375</v>
+        <v>177.4315880782802</v>
       </c>
     </row>
     <row r="14">
@@ -5245,22 +5245,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>735.7608039158875</v>
+        <v>886.7385733628859</v>
       </c>
       <c r="C14" t="n">
-        <v>535.2814319532674</v>
+        <v>849.3211162073476</v>
       </c>
       <c r="D14" t="n">
-        <v>374.332789791803</v>
+        <v>688.3724740458831</v>
       </c>
       <c r="E14" t="n">
-        <v>219.4203760474911</v>
+        <v>533.4600603015713</v>
       </c>
       <c r="F14" t="n">
-        <v>219.4203760474911</v>
+        <v>378.015990899539</v>
       </c>
       <c r="G14" t="n">
-        <v>65.12</v>
+        <v>223.7156148520479</v>
       </c>
       <c r="H14" t="n">
         <v>65.12</v>
@@ -5281,10 +5281,10 @@
         <v>1285.675195076803</v>
       </c>
       <c r="N14" t="n">
-        <v>1644.28</v>
+        <v>1898.895514851567</v>
       </c>
       <c r="O14" t="n">
-        <v>2450.14</v>
+        <v>2704.755514851567</v>
       </c>
       <c r="P14" t="n">
         <v>3256</v>
@@ -5345,22 +5345,22 @@
         <v>65.12</v>
       </c>
       <c r="I15" t="n">
-        <v>65.12</v>
+        <v>98.65487796756496</v>
       </c>
       <c r="J15" t="n">
-        <v>437.5665201752989</v>
+        <v>222.6113981428639</v>
       </c>
       <c r="K15" t="n">
-        <v>626.7593362696823</v>
+        <v>660.2942142372473</v>
       </c>
       <c r="L15" t="n">
-        <v>1146.599797864882</v>
+        <v>931.6446758324473</v>
       </c>
       <c r="M15" t="n">
-        <v>1430.751526182163</v>
+        <v>1017.725217575307</v>
       </c>
       <c r="N15" t="n">
-        <v>1564.031810789731</v>
+        <v>1315.541810789732</v>
       </c>
       <c r="O15" t="n">
         <v>1803.074262473451</v>
@@ -5445,13 +5445,13 @@
         <v>599.0397446017254</v>
       </c>
       <c r="P16" t="n">
-        <v>599.0397446017254</v>
+        <v>158.1832826539703</v>
       </c>
       <c r="Q16" t="n">
-        <v>599.0397446017254</v>
+        <v>65.12</v>
       </c>
       <c r="R16" t="n">
-        <v>177.6184643463186</v>
+        <v>65.12</v>
       </c>
       <c r="S16" t="n">
         <v>65.12</v>
@@ -5509,16 +5509,16 @@
         <v>456.4291130376557</v>
       </c>
       <c r="K17" t="n">
-        <v>887.4717564436343</v>
+        <v>1166.135479385524</v>
       </c>
       <c r="L17" t="n">
-        <v>1693.331756443634</v>
+        <v>1166.135479385524</v>
       </c>
       <c r="M17" t="n">
-        <v>2204.180585172569</v>
+        <v>1676.984308114459</v>
       </c>
       <c r="N17" t="n">
-        <v>2817.400904947332</v>
+        <v>2290.204627889222</v>
       </c>
       <c r="O17" t="n">
         <v>2817.400904947332</v>
@@ -5588,22 +5588,22 @@
         <v>189.076520175299</v>
       </c>
       <c r="K18" t="n">
-        <v>654.4793362696823</v>
+        <v>378.2693362696824</v>
       </c>
       <c r="L18" t="n">
-        <v>925.8297978648825</v>
+        <v>649.6197978648825</v>
       </c>
       <c r="M18" t="n">
-        <v>1011.910339607742</v>
+        <v>735.7003396077417</v>
       </c>
       <c r="N18" t="n">
-        <v>1421.40062421531</v>
+        <v>868.9806242153101</v>
       </c>
       <c r="O18" t="n">
-        <v>1704.463365791451</v>
+        <v>1323.391838231026</v>
       </c>
       <c r="P18" t="n">
-        <v>1816.992710260958</v>
+        <v>1712.131182700533</v>
       </c>
       <c r="Q18" t="n">
         <v>1816.992710260958</v>
@@ -5640,76 +5640,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2821.238164931536</v>
+        <v>422.5399739669084</v>
       </c>
       <c r="C19" t="n">
-        <v>2827.450170749972</v>
+        <v>428.7519797853442</v>
       </c>
       <c r="D19" t="n">
-        <v>2827.450170749972</v>
+        <v>428.7519797853442</v>
       </c>
       <c r="E19" t="n">
-        <v>2825.449256773248</v>
+        <v>428.7519797853442</v>
       </c>
       <c r="F19" t="n">
-        <v>2830.020229365183</v>
+        <v>433.3229523772797</v>
       </c>
       <c r="G19" t="n">
-        <v>2863.636795252069</v>
+        <v>466.939518264165</v>
       </c>
       <c r="H19" t="n">
-        <v>2913.363380411466</v>
+        <v>516.6661034235625</v>
       </c>
       <c r="I19" t="n">
-        <v>3014.706259347549</v>
+        <v>618.0089823596454</v>
       </c>
       <c r="J19" t="n">
-        <v>3256</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="K19" t="n">
-        <v>3256</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="L19" t="n">
-        <v>3256</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="M19" t="n">
-        <v>3256</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="N19" t="n">
-        <v>2960.863560331632</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="O19" t="n">
-        <v>2960.863560331632</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="P19" t="n">
-        <v>2960.863560331632</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="Q19" t="n">
-        <v>2509.51076596234</v>
+        <v>517.2433615971223</v>
       </c>
       <c r="R19" t="n">
-        <v>2509.51076596234</v>
+        <v>65.12</v>
       </c>
       <c r="S19" t="n">
-        <v>2463.818190964628</v>
+        <v>65.12</v>
       </c>
       <c r="T19" t="n">
-        <v>2532.103870123432</v>
+        <v>133.4056791588049</v>
       </c>
       <c r="U19" t="n">
-        <v>2658.865062761719</v>
+        <v>260.1668717970915</v>
       </c>
       <c r="V19" t="n">
-        <v>2737.896455647665</v>
+        <v>339.1982646830375</v>
       </c>
       <c r="W19" t="n">
-        <v>2789.997373907342</v>
+        <v>391.2991829427149</v>
       </c>
       <c r="X19" t="n">
-        <v>2821.238164931536</v>
+        <v>422.5399739669084</v>
       </c>
       <c r="Y19" t="n">
-        <v>2821.238164931536</v>
+        <v>422.5399739669084</v>
       </c>
     </row>
     <row r="20">
@@ -5719,10 +5719,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>879.6685602764463</v>
+        <v>880.1035184729978</v>
       </c>
       <c r="C20" t="n">
-        <v>707.4720165966545</v>
+        <v>707.906974793206</v>
       </c>
       <c r="D20" t="n">
         <v>575.2411609145698</v>
@@ -5746,13 +5746,13 @@
         <v>456.4291130376557</v>
       </c>
       <c r="K20" t="n">
-        <v>1166.135479385524</v>
+        <v>694.8320762183973</v>
       </c>
       <c r="L20" t="n">
-        <v>1166.135479385524</v>
+        <v>1500.692076218397</v>
       </c>
       <c r="M20" t="n">
-        <v>1676.984308114459</v>
+        <v>2011.540904947332</v>
       </c>
       <c r="N20" t="n">
         <v>2011.540904947332</v>
@@ -5767,28 +5767,28 @@
         <v>3256</v>
       </c>
       <c r="R20" t="n">
-        <v>3256</v>
+        <v>3256.000000000055</v>
       </c>
       <c r="S20" t="n">
-        <v>3037.971547674421</v>
+        <v>3037.971547674476</v>
       </c>
       <c r="T20" t="n">
-        <v>2727.188131786983</v>
+        <v>2727.188131787037</v>
       </c>
       <c r="U20" t="n">
-        <v>2353.227226182325</v>
+        <v>2353.22722618238</v>
       </c>
       <c r="V20" t="n">
-        <v>1998.832252276443</v>
+        <v>1999.267210472994</v>
       </c>
       <c r="W20" t="n">
-        <v>1635.828741184576</v>
+        <v>1636.263699381128</v>
       </c>
       <c r="X20" t="n">
-        <v>1319.382444759659</v>
+        <v>1319.817402956211</v>
       </c>
       <c r="Y20" t="n">
-        <v>1084.718371342683</v>
+        <v>1085.153329539235</v>
       </c>
     </row>
     <row r="21">
@@ -5798,76 +5798,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1883.171291723345</v>
+        <v>444.164001984303</v>
       </c>
       <c r="C21" t="n">
-        <v>1800.242087232921</v>
+        <v>361.2347974938795</v>
       </c>
       <c r="D21" t="n">
-        <v>1730.608060063525</v>
+        <v>291.6007703244828</v>
       </c>
       <c r="E21" t="n">
-        <v>1666.292810344421</v>
+        <v>227.2855206053791</v>
       </c>
       <c r="F21" t="n">
-        <v>1605.044080710202</v>
+        <v>166.0367909711601</v>
       </c>
       <c r="G21" t="n">
-        <v>1557.832428311185</v>
+        <v>118.8251385721426</v>
       </c>
       <c r="H21" t="n">
-        <v>1504.127289739042</v>
+        <v>65.12</v>
       </c>
       <c r="I21" t="n">
-        <v>1565.382167706607</v>
+        <v>126.374877967565</v>
       </c>
       <c r="J21" t="n">
-        <v>1689.338687881906</v>
+        <v>250.3313981428639</v>
       </c>
       <c r="K21" t="n">
-        <v>1878.53150397629</v>
+        <v>439.5242142372473</v>
       </c>
       <c r="L21" t="n">
-        <v>2149.88196557149</v>
+        <v>710.8746758324473</v>
       </c>
       <c r="M21" t="n">
-        <v>2235.962507314349</v>
+        <v>796.9552175753066</v>
       </c>
       <c r="N21" t="n">
-        <v>2369.242791921917</v>
+        <v>930.2355021828749</v>
       </c>
       <c r="O21" t="n">
-        <v>2884.495243605636</v>
+        <v>1445.487953866594</v>
       </c>
       <c r="P21" t="n">
-        <v>3256</v>
+        <v>1816.992710260958</v>
       </c>
       <c r="Q21" t="n">
-        <v>3256</v>
+        <v>1816.992710260958</v>
       </c>
       <c r="R21" t="n">
-        <v>2985.016366371334</v>
+        <v>1546.009076632292</v>
       </c>
       <c r="S21" t="n">
-        <v>2795.557780548494</v>
+        <v>1356.550490809452</v>
       </c>
       <c r="T21" t="n">
-        <v>2667.923674268177</v>
+        <v>1228.916384529135</v>
       </c>
       <c r="U21" t="n">
-        <v>2545.488967439705</v>
+        <v>1106.481677700664</v>
       </c>
       <c r="V21" t="n">
-        <v>2408.609505630089</v>
+        <v>969.6022158910475</v>
       </c>
       <c r="W21" t="n">
-        <v>2253.687139054505</v>
+        <v>814.6798493154631</v>
       </c>
       <c r="X21" t="n">
-        <v>2111.401543655124</v>
+        <v>672.3942539160818</v>
       </c>
       <c r="Y21" t="n">
-        <v>1989.794076214584</v>
+        <v>550.786786475542</v>
       </c>
     </row>
     <row r="22">
@@ -5877,55 +5877,55 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>413.989112502805</v>
+        <v>422.5399739669084</v>
       </c>
       <c r="C22" t="n">
-        <v>420.2011183212408</v>
+        <v>428.7519797853442</v>
       </c>
       <c r="D22" t="n">
-        <v>420.2011183212408</v>
+        <v>428.7519797853442</v>
       </c>
       <c r="E22" t="n">
-        <v>420.2011183212408</v>
+        <v>428.7519797853442</v>
       </c>
       <c r="F22" t="n">
-        <v>424.7720909131763</v>
+        <v>433.3229523772797</v>
       </c>
       <c r="G22" t="n">
-        <v>458.3886568000616</v>
+        <v>466.939518264165</v>
       </c>
       <c r="H22" t="n">
-        <v>508.1152419594592</v>
+        <v>516.6661034235625</v>
       </c>
       <c r="I22" t="n">
-        <v>609.4581208955422</v>
+        <v>618.0089823596454</v>
       </c>
       <c r="J22" t="n">
-        <v>850.7518615479935</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="K22" t="n">
-        <v>850.7518615479935</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="L22" t="n">
-        <v>850.7518615479935</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="M22" t="n">
-        <v>850.7518615479935</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="N22" t="n">
-        <v>850.7518615479935</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="O22" t="n">
-        <v>850.7518615479935</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="P22" t="n">
-        <v>438.1782278830667</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="Q22" t="n">
-        <v>65.12</v>
+        <v>601.4589976606127</v>
       </c>
       <c r="R22" t="n">
-        <v>65.12</v>
+        <v>149.3356360634903</v>
       </c>
       <c r="S22" t="n">
         <v>65.12</v>
@@ -5946,7 +5946,7 @@
         <v>422.5399739669084</v>
       </c>
       <c r="Y22" t="n">
-        <v>413.989112502805</v>
+        <v>422.5399739669084</v>
       </c>
     </row>
     <row r="23">
@@ -5956,22 +5956,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>879.6685602765154</v>
+        <v>880.1035184729978</v>
       </c>
       <c r="C23" t="n">
-        <v>707.4720165967236</v>
+        <v>707.906974793206</v>
       </c>
       <c r="D23" t="n">
-        <v>574.8062027180874</v>
+        <v>575.2411609145698</v>
       </c>
       <c r="E23" t="n">
-        <v>448.1766172566039</v>
+        <v>448.6115754530863</v>
       </c>
       <c r="F23" t="n">
-        <v>321.0153761374</v>
+        <v>321.4503343338824</v>
       </c>
       <c r="G23" t="n">
-        <v>194.9978283727372</v>
+        <v>195.4327865692196</v>
       </c>
       <c r="H23" t="n">
         <v>65.12</v>
@@ -5986,46 +5986,46 @@
         <v>1166.135479385524</v>
       </c>
       <c r="L23" t="n">
-        <v>1644.28</v>
+        <v>1166.135479385524</v>
       </c>
       <c r="M23" t="n">
-        <v>1644.28</v>
+        <v>1676.984308114459</v>
       </c>
       <c r="N23" t="n">
-        <v>1644.28</v>
+        <v>2290.204627889222</v>
       </c>
       <c r="O23" t="n">
-        <v>2450.14</v>
+        <v>2290.204627889222</v>
       </c>
       <c r="P23" t="n">
-        <v>3256</v>
+        <v>2817.400904947332</v>
       </c>
       <c r="Q23" t="n">
         <v>3256</v>
       </c>
       <c r="R23" t="n">
-        <v>3256.000000000069</v>
+        <v>3256</v>
       </c>
       <c r="S23" t="n">
-        <v>3037.97154767449</v>
+        <v>3037.971547674421</v>
       </c>
       <c r="T23" t="n">
-        <v>2727.188131787052</v>
+        <v>2727.188131786983</v>
       </c>
       <c r="U23" t="n">
-        <v>2353.227226182395</v>
+        <v>2353.227226182325</v>
       </c>
       <c r="V23" t="n">
-        <v>1998.832252276512</v>
+        <v>1998.832252276443</v>
       </c>
       <c r="W23" t="n">
-        <v>1635.828741184645</v>
+        <v>1636.263699381128</v>
       </c>
       <c r="X23" t="n">
-        <v>1319.382444759729</v>
+        <v>1319.817402956211</v>
       </c>
       <c r="Y23" t="n">
-        <v>1084.718371342752</v>
+        <v>1085.153329539235</v>
       </c>
     </row>
     <row r="24">
@@ -6065,19 +6065,19 @@
         <v>439.5242142372473</v>
       </c>
       <c r="L24" t="n">
-        <v>710.8746758324473</v>
+        <v>987.0846758324475</v>
       </c>
       <c r="M24" t="n">
         <v>1073.165217575307</v>
       </c>
       <c r="N24" t="n">
-        <v>1206.445502182875</v>
+        <v>1360.559386547307</v>
       </c>
       <c r="O24" t="n">
-        <v>1704.463365791451</v>
+        <v>1599.601838231026</v>
       </c>
       <c r="P24" t="n">
-        <v>1816.992710260958</v>
+        <v>1712.131182700533</v>
       </c>
       <c r="Q24" t="n">
         <v>1816.992710260958</v>
@@ -6114,55 +6114,55 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>414.6002565978003</v>
+        <v>422.5399739669084</v>
       </c>
       <c r="C25" t="n">
-        <v>420.8122624162361</v>
+        <v>428.7519797853442</v>
       </c>
       <c r="D25" t="n">
-        <v>414.210021956079</v>
+        <v>428.7519797853442</v>
       </c>
       <c r="E25" t="n">
-        <v>414.210021956079</v>
+        <v>428.7519797853442</v>
       </c>
       <c r="F25" t="n">
-        <v>418.7809945480145</v>
+        <v>433.3229523772797</v>
       </c>
       <c r="G25" t="n">
-        <v>452.3975604348998</v>
+        <v>466.939518264165</v>
       </c>
       <c r="H25" t="n">
-        <v>502.1241455942974</v>
+        <v>516.6661034235625</v>
       </c>
       <c r="I25" t="n">
-        <v>603.4670245303803</v>
+        <v>618.0089823596454</v>
       </c>
       <c r="J25" t="n">
-        <v>844.7607651828316</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="K25" t="n">
-        <v>844.7607651828316</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="L25" t="n">
-        <v>844.7607651828316</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="M25" t="n">
-        <v>600.6884304327813</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="N25" t="n">
-        <v>600.6884304327813</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="O25" t="n">
-        <v>600.6884304327813</v>
+        <v>494.2061936393544</v>
       </c>
       <c r="P25" t="n">
-        <v>600.6884304327813</v>
+        <v>81.63255997442758</v>
       </c>
       <c r="Q25" t="n">
-        <v>149.3356360634903</v>
+        <v>81.63255997442758</v>
       </c>
       <c r="R25" t="n">
-        <v>149.3356360634903</v>
+        <v>65.12</v>
       </c>
       <c r="S25" t="n">
         <v>65.12</v>
@@ -6193,19 +6193,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>656.9683066562752</v>
+        <v>512.760190708043</v>
       </c>
       <c r="C26" t="n">
-        <v>430.2263084310288</v>
+        <v>286.0181924827966</v>
       </c>
       <c r="D26" t="n">
-        <v>243.0150400069381</v>
+        <v>242.4030023101174</v>
       </c>
       <c r="E26" t="n">
-        <v>61.84</v>
+        <v>242.4030023101174</v>
       </c>
       <c r="F26" t="n">
-        <v>61.84</v>
+        <v>242.4030023101174</v>
       </c>
       <c r="G26" t="n">
         <v>61.84</v>
@@ -6217,22 +6217,22 @@
         <v>61.84</v>
       </c>
       <c r="J26" t="n">
-        <v>61.84</v>
+        <v>453.1491130376558</v>
       </c>
       <c r="K26" t="n">
-        <v>771.5463663478683</v>
+        <v>453.1491130376558</v>
       </c>
       <c r="L26" t="n">
-        <v>1536.816366347868</v>
+        <v>1122.86090494728</v>
       </c>
       <c r="M26" t="n">
-        <v>1536.816366347868</v>
+        <v>1122.86090494728</v>
       </c>
       <c r="N26" t="n">
-        <v>1536.816366347868</v>
+        <v>1122.86090494728</v>
       </c>
       <c r="O26" t="n">
-        <v>2302.086366347896</v>
+        <v>1888.130904947306</v>
       </c>
       <c r="P26" t="n">
         <v>2653.400904947332</v>
@@ -6253,16 +6253,16 @@
         <v>1999.450863729503</v>
       </c>
       <c r="V26" t="n">
-        <v>1734.718551226398</v>
+        <v>1590.510435278166</v>
       </c>
       <c r="W26" t="n">
-        <v>1317.169585589077</v>
+        <v>1172.961469640845</v>
       </c>
       <c r="X26" t="n">
-        <v>946.1778346187059</v>
+        <v>801.9697186704736</v>
       </c>
       <c r="Y26" t="n">
-        <v>656.9683066562752</v>
+        <v>512.760190708043</v>
       </c>
     </row>
     <row r="27">
@@ -6305,10 +6305,10 @@
         <v>1322.384675832448</v>
       </c>
       <c r="M27" t="n">
-        <v>1427.390920121557</v>
+        <v>1631.215217575307</v>
       </c>
       <c r="N27" t="n">
-        <v>1783.421204729126</v>
+        <v>1987.245502182875</v>
       </c>
       <c r="O27" t="n">
         <v>2245.213656412845</v>
@@ -6351,52 +6351,52 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>175.5382646830375</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="C28" t="n">
-        <v>175.5382646830375</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="D28" t="n">
-        <v>175.5382646830375</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="E28" t="n">
-        <v>175.5382646830375</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="F28" t="n">
-        <v>125.6565919883487</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="G28" t="n">
-        <v>125.6565919883487</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="H28" t="n">
-        <v>121.8473737038854</v>
+        <v>170.342369793817</v>
       </c>
       <c r="I28" t="n">
-        <v>169.7302526399683</v>
+        <v>218.2252487298999</v>
       </c>
       <c r="J28" t="n">
-        <v>357.5639932924196</v>
+        <v>406.0589893823512</v>
       </c>
       <c r="K28" t="n">
-        <v>357.5639932924196</v>
+        <v>406.0589893823512</v>
       </c>
       <c r="L28" t="n">
-        <v>357.5639932924196</v>
+        <v>406.0589893823512</v>
       </c>
       <c r="M28" t="n">
-        <v>357.5639932924196</v>
+        <v>406.0589893823512</v>
       </c>
       <c r="N28" t="n">
-        <v>357.5639932924196</v>
+        <v>406.0589893823512</v>
       </c>
       <c r="O28" t="n">
-        <v>61.84</v>
+        <v>406.0589893823512</v>
       </c>
       <c r="P28" t="n">
-        <v>61.84</v>
+        <v>406.0589893823512</v>
       </c>
       <c r="Q28" t="n">
-        <v>61.84</v>
+        <v>406.0589893823512</v>
       </c>
       <c r="R28" t="n">
         <v>61.84</v>
@@ -6414,13 +6414,13 @@
         <v>175.5382646830375</v>
       </c>
       <c r="W28" t="n">
-        <v>175.5382646830375</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="X28" t="n">
-        <v>175.5382646830375</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="Y28" t="n">
-        <v>175.5382646830375</v>
+        <v>174.1515880782802</v>
       </c>
     </row>
     <row r="29">
@@ -6430,22 +6430,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1204.096245745725</v>
+        <v>512.760190708043</v>
       </c>
       <c r="C29" t="n">
-        <v>977.3542475204788</v>
+        <v>286.0181924827966</v>
       </c>
       <c r="D29" t="n">
-        <v>790.1429790963881</v>
+        <v>98.80692405870585</v>
       </c>
       <c r="E29" t="n">
-        <v>608.9679390894501</v>
+        <v>98.80692405870585</v>
       </c>
       <c r="F29" t="n">
-        <v>427.2612434247916</v>
+        <v>98.80692405870585</v>
       </c>
       <c r="G29" t="n">
-        <v>246.6982411146742</v>
+        <v>98.80692405870585</v>
       </c>
       <c r="H29" t="n">
         <v>61.84</v>
@@ -6466,40 +6466,40 @@
         <v>1673.704308114459</v>
       </c>
       <c r="N29" t="n">
-        <v>1888.130904947298</v>
+        <v>2286.924627889222</v>
       </c>
       <c r="O29" t="n">
-        <v>2653.400904947332</v>
+        <v>3052.194627889256</v>
       </c>
       <c r="P29" t="n">
-        <v>2653.400904947332</v>
+        <v>3092</v>
       </c>
       <c r="Q29" t="n">
         <v>3092</v>
       </c>
       <c r="R29" t="n">
-        <v>3075.681720898853</v>
+        <v>3065.860001183541</v>
       </c>
       <c r="S29" t="n">
-        <v>3075.681720898853</v>
+        <v>2793.286094312508</v>
       </c>
       <c r="T29" t="n">
-        <v>2710.35285046596</v>
+        <v>2427.957223879615</v>
       </c>
       <c r="U29" t="n">
-        <v>2281.846490315848</v>
+        <v>1999.450863729503</v>
       </c>
       <c r="V29" t="n">
-        <v>2281.846490315848</v>
+        <v>1590.510435278166</v>
       </c>
       <c r="W29" t="n">
-        <v>1864.297524678527</v>
+        <v>1172.961469640845</v>
       </c>
       <c r="X29" t="n">
-        <v>1493.305773708156</v>
+        <v>801.9697186704736</v>
       </c>
       <c r="Y29" t="n">
-        <v>1204.096245745725</v>
+        <v>512.760190708043</v>
       </c>
     </row>
     <row r="30">
@@ -6545,10 +6545,10 @@
         <v>1631.215217575307</v>
       </c>
       <c r="N30" t="n">
-        <v>1987.245502182875</v>
+        <v>1783.421204729126</v>
       </c>
       <c r="O30" t="n">
-        <v>2449.037953866594</v>
+        <v>2245.213656412845</v>
       </c>
       <c r="P30" t="n">
         <v>2580.493000882351</v>
@@ -6588,52 +6588,52 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>111.0552720687223</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="C31" t="n">
-        <v>111.0552720687223</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="D31" t="n">
-        <v>111.0552720687223</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="E31" t="n">
-        <v>111.0552720687223</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="F31" t="n">
-        <v>111.0552720687223</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="G31" t="n">
-        <v>90.80893586515658</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="H31" t="n">
-        <v>86.99971758069333</v>
+        <v>170.342369793817</v>
       </c>
       <c r="I31" t="n">
-        <v>134.8825965167762</v>
+        <v>218.2252487298999</v>
       </c>
       <c r="J31" t="n">
-        <v>322.7163371692276</v>
+        <v>406.0589893823512</v>
       </c>
       <c r="K31" t="n">
-        <v>258.5539393902952</v>
+        <v>406.0589893823512</v>
       </c>
       <c r="L31" t="n">
-        <v>258.5539393902952</v>
+        <v>406.0589893823512</v>
       </c>
       <c r="M31" t="n">
-        <v>258.5539393902952</v>
+        <v>406.0589893823512</v>
       </c>
       <c r="N31" t="n">
-        <v>258.5539393902952</v>
+        <v>406.0589893823512</v>
       </c>
       <c r="O31" t="n">
-        <v>258.5539393902952</v>
+        <v>406.0589893823512</v>
       </c>
       <c r="P31" t="n">
-        <v>258.5539393902952</v>
+        <v>61.84</v>
       </c>
       <c r="Q31" t="n">
-        <v>258.5539393902952</v>
+        <v>61.84</v>
       </c>
       <c r="R31" t="n">
         <v>61.84</v>
@@ -6657,7 +6657,7 @@
         <v>174.1515880782802</v>
       </c>
       <c r="Y31" t="n">
-        <v>111.0552720687223</v>
+        <v>174.1515880782802</v>
       </c>
     </row>
     <row r="32">
@@ -6667,49 +6667,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>812.6382572461436</v>
+        <v>804.0962457457251</v>
       </c>
       <c r="C32" t="n">
-        <v>652.5629256875638</v>
+        <v>644.0209141871454</v>
       </c>
       <c r="D32" t="n">
-        <v>532.0183239301398</v>
+        <v>523.4763124297214</v>
       </c>
       <c r="E32" t="n">
-        <v>417.5099505898684</v>
+        <v>408.96793908945</v>
       </c>
       <c r="F32" t="n">
-        <v>302.4699215918766</v>
+        <v>293.9279100914582</v>
       </c>
       <c r="G32" t="n">
-        <v>188.5735859484259</v>
+        <v>180.0315744480075</v>
       </c>
       <c r="H32" t="n">
-        <v>70.38201150041843</v>
+        <v>61.84</v>
       </c>
       <c r="I32" t="n">
         <v>61.84</v>
       </c>
       <c r="J32" t="n">
-        <v>445.5561922637025</v>
+        <v>445.5561922637026</v>
       </c>
       <c r="K32" t="n">
-        <v>430.9405883765121</v>
+        <v>1155.05686870288</v>
       </c>
       <c r="L32" t="n">
-        <v>639.3486799493101</v>
+        <v>1852.123113224189</v>
       </c>
       <c r="M32" t="n">
-        <v>1145.031728341244</v>
+        <v>2357.806161616123</v>
       </c>
       <c r="N32" t="n">
-        <v>1129.493647533162</v>
+        <v>2342.268080808041</v>
       </c>
       <c r="O32" t="n">
-        <v>1894.763647533204</v>
+        <v>2326.72999999996</v>
       </c>
       <c r="P32" t="n">
-        <v>2660.033647533245</v>
+        <v>3092</v>
       </c>
       <c r="Q32" t="n">
         <v>3092</v>
@@ -6736,7 +6736,7 @@
         <v>1228.109717486932</v>
       </c>
       <c r="Y32" t="n">
-        <v>1005.566856191168</v>
+        <v>997.0248446907499</v>
       </c>
     </row>
     <row r="33">
@@ -6770,25 +6770,25 @@
         <v>61.84</v>
       </c>
       <c r="J33" t="n">
-        <v>312.3286282495397</v>
+        <v>185.796520175299</v>
       </c>
       <c r="K33" t="n">
-        <v>501.5214443439232</v>
+        <v>374.9893362696823</v>
       </c>
       <c r="L33" t="n">
-        <v>772.8719059391233</v>
+        <v>934.4297978648825</v>
       </c>
       <c r="M33" t="n">
-        <v>1147.042447681983</v>
+        <v>1020.510339607742</v>
       </c>
       <c r="N33" t="n">
-        <v>1280.322732289551</v>
+        <v>1163.581204729126</v>
       </c>
       <c r="O33" t="n">
-        <v>1519.36518397327</v>
+        <v>1402.623656412844</v>
       </c>
       <c r="P33" t="n">
-        <v>1631.894528442776</v>
+        <v>1515.153000882351</v>
       </c>
       <c r="Q33" t="n">
         <v>1631.894528442776</v>
@@ -6825,52 +6825,52 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>486.0066123122566</v>
+        <v>486.0066123122328</v>
       </c>
       <c r="C34" t="n">
-        <v>504.0986181306923</v>
+        <v>504.0986181306686</v>
       </c>
       <c r="D34" t="n">
-        <v>509.5077622556924</v>
+        <v>509.5077622556687</v>
       </c>
       <c r="E34" t="n">
-        <v>519.4266664671054</v>
+        <v>519.4266664670818</v>
       </c>
       <c r="F34" t="n">
-        <v>535.8776390590409</v>
+        <v>535.8776390590173</v>
       </c>
       <c r="G34" t="n">
-        <v>581.3742049459262</v>
+        <v>581.3742049459025</v>
       </c>
       <c r="H34" t="n">
-        <v>642.9807901053238</v>
+        <v>642.9807901053001</v>
       </c>
       <c r="I34" t="n">
-        <v>756.2036690414067</v>
+        <v>756.203669041383</v>
       </c>
       <c r="J34" t="n">
-        <v>1009.377409693858</v>
+        <v>1009.377409693834</v>
       </c>
       <c r="K34" t="n">
-        <v>1011.831843630726</v>
+        <v>1011.831843630703</v>
       </c>
       <c r="L34" t="n">
-        <v>877.9453505420606</v>
+        <v>1011.831843630703</v>
       </c>
       <c r="M34" t="n">
-        <v>645.9942279132224</v>
+        <v>1011.831843630703</v>
       </c>
       <c r="N34" t="n">
-        <v>645.9942279132224</v>
+        <v>1011.831843630703</v>
       </c>
       <c r="O34" t="n">
-        <v>293.0189106616921</v>
+        <v>1011.831843630703</v>
       </c>
       <c r="P34" t="n">
-        <v>293.0189106616921</v>
+        <v>941.0737317239891</v>
       </c>
       <c r="Q34" t="n">
-        <v>293.0189106616921</v>
+        <v>501.8421494759102</v>
       </c>
       <c r="R34" t="n">
         <v>61.84</v>
@@ -6904,46 +6904,46 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>812.6382572461436</v>
+        <v>804.0962457457251</v>
       </c>
       <c r="C35" t="n">
-        <v>652.5629256875638</v>
+        <v>644.0209141871454</v>
       </c>
       <c r="D35" t="n">
-        <v>532.0183239301398</v>
+        <v>523.4763124297214</v>
       </c>
       <c r="E35" t="n">
-        <v>417.5099505898684</v>
+        <v>408.96793908945</v>
       </c>
       <c r="F35" t="n">
-        <v>302.4699215918766</v>
+        <v>293.9279100914582</v>
       </c>
       <c r="G35" t="n">
-        <v>188.5735859484259</v>
+        <v>180.0315744480075</v>
       </c>
       <c r="H35" t="n">
-        <v>70.38201150041843</v>
+        <v>61.84</v>
       </c>
       <c r="I35" t="n">
         <v>61.84</v>
       </c>
       <c r="J35" t="n">
-        <v>445.5561922637025</v>
+        <v>61.84</v>
       </c>
       <c r="K35" t="n">
-        <v>1155.056868702875</v>
+        <v>77.37808080808094</v>
       </c>
       <c r="L35" t="n">
-        <v>1139.518787894794</v>
+        <v>61.84</v>
       </c>
       <c r="M35" t="n">
-        <v>1645.201836286727</v>
+        <v>519.3605521604707</v>
       </c>
       <c r="N35" t="n">
-        <v>1629.663755478645</v>
+        <v>1129.493647533149</v>
       </c>
       <c r="O35" t="n">
-        <v>2394.933755478694</v>
+        <v>1894.763647533197</v>
       </c>
       <c r="P35" t="n">
         <v>2660.033647533245</v>
@@ -6973,7 +6973,7 @@
         <v>1228.109717486932</v>
       </c>
       <c r="Y35" t="n">
-        <v>1005.566856191168</v>
+        <v>997.0248446907499</v>
       </c>
     </row>
     <row r="36">
@@ -7004,25 +7004,25 @@
         <v>61.84</v>
       </c>
       <c r="I36" t="n">
-        <v>61.84</v>
+        <v>134.974877967565</v>
       </c>
       <c r="J36" t="n">
-        <v>185.796520175299</v>
+        <v>258.9313981428639</v>
       </c>
       <c r="K36" t="n">
-        <v>374.9893362696823</v>
+        <v>672.869916783498</v>
       </c>
       <c r="L36" t="n">
-        <v>656.130378378698</v>
+        <v>944.220378378698</v>
       </c>
       <c r="M36" t="n">
-        <v>742.2109201215573</v>
+        <v>1030.300920121557</v>
       </c>
       <c r="N36" t="n">
-        <v>875.4912047291256</v>
+        <v>1163.581204729126</v>
       </c>
       <c r="O36" t="n">
-        <v>1114.533656412844</v>
+        <v>1402.623656412844</v>
       </c>
       <c r="P36" t="n">
         <v>1515.153000882351</v>
@@ -7062,52 +7062,52 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>486.0066123122566</v>
+        <v>486.0066123122328</v>
       </c>
       <c r="C37" t="n">
-        <v>504.0986181306923</v>
+        <v>504.0986181306686</v>
       </c>
       <c r="D37" t="n">
-        <v>509.5077622556924</v>
+        <v>509.5077622556687</v>
       </c>
       <c r="E37" t="n">
-        <v>519.4266664671054</v>
+        <v>519.4266664670818</v>
       </c>
       <c r="F37" t="n">
-        <v>535.8776390590409</v>
+        <v>535.8776390590173</v>
       </c>
       <c r="G37" t="n">
-        <v>581.3742049459262</v>
+        <v>581.3742049459025</v>
       </c>
       <c r="H37" t="n">
-        <v>642.9807901053238</v>
+        <v>642.9807901053001</v>
       </c>
       <c r="I37" t="n">
-        <v>756.2036690414067</v>
+        <v>756.203669041383</v>
       </c>
       <c r="J37" t="n">
-        <v>1009.377409693858</v>
+        <v>1009.377409693834</v>
       </c>
       <c r="K37" t="n">
-        <v>1011.831843630726</v>
+        <v>1011.831843630703</v>
       </c>
       <c r="L37" t="n">
-        <v>1011.831843630726</v>
+        <v>877.945350542037</v>
       </c>
       <c r="M37" t="n">
-        <v>779.8807210018881</v>
+        <v>645.9942279131988</v>
       </c>
       <c r="N37" t="n">
-        <v>501.8421494759102</v>
+        <v>362.9790003660423</v>
       </c>
       <c r="O37" t="n">
-        <v>501.8421494759102</v>
+        <v>61.84</v>
       </c>
       <c r="P37" t="n">
-        <v>501.8421494759102</v>
+        <v>61.84</v>
       </c>
       <c r="Q37" t="n">
-        <v>501.8421494759102</v>
+        <v>61.84</v>
       </c>
       <c r="R37" t="n">
         <v>61.84</v>
@@ -7141,19 +7141,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>812.6382572461436</v>
+        <v>804.0962457457251</v>
       </c>
       <c r="C38" t="n">
-        <v>652.5629256875638</v>
+        <v>644.0209141871454</v>
       </c>
       <c r="D38" t="n">
-        <v>532.0183239301398</v>
+        <v>523.4763124297214</v>
       </c>
       <c r="E38" t="n">
-        <v>417.5099505898684</v>
+        <v>408.96793908945</v>
       </c>
       <c r="F38" t="n">
-        <v>302.4699215918766</v>
+        <v>293.9279100914582</v>
       </c>
       <c r="G38" t="n">
         <v>180.0315744480075</v>
@@ -7171,19 +7171,19 @@
         <v>430.0181114556214</v>
       </c>
       <c r="L38" t="n">
-        <v>1071.315032416037</v>
+        <v>794.4855845766606</v>
       </c>
       <c r="M38" t="n">
-        <v>1576.99808080797</v>
+        <v>1300.168632968594</v>
       </c>
       <c r="N38" t="n">
-        <v>1561.459999999888</v>
+        <v>1910.301728341273</v>
       </c>
       <c r="O38" t="n">
-        <v>2326.729999999944</v>
+        <v>1894.763647533191</v>
       </c>
       <c r="P38" t="n">
-        <v>3092</v>
+        <v>2660.033647533246</v>
       </c>
       <c r="Q38" t="n">
         <v>3092</v>
@@ -7192,25 +7192,25 @@
         <v>3092</v>
       </c>
       <c r="S38" t="n">
-        <v>2886.092759795633</v>
+        <v>2877.550748295214</v>
       </c>
       <c r="T38" t="n">
-        <v>2587.430556029407</v>
+        <v>2578.888544528988</v>
       </c>
       <c r="U38" t="n">
-        <v>2225.590862545962</v>
+        <v>2217.048851045543</v>
       </c>
       <c r="V38" t="n">
-        <v>1883.317100761291</v>
+        <v>1874.775089260873</v>
       </c>
       <c r="W38" t="n">
-        <v>1532.434801790637</v>
+        <v>1523.892790290219</v>
       </c>
       <c r="X38" t="n">
-        <v>1228.109717486932</v>
+        <v>1219.567705986514</v>
       </c>
       <c r="Y38" t="n">
-        <v>1005.566856191168</v>
+        <v>997.0248446907499</v>
       </c>
     </row>
     <row r="39">
@@ -7259,10 +7259,10 @@
         <v>938.8355021828751</v>
       </c>
       <c r="O39" t="n">
-        <v>1465.967953866594</v>
+        <v>1177.877953866594</v>
       </c>
       <c r="P39" t="n">
-        <v>1578.497298336101</v>
+        <v>1515.153000882351</v>
       </c>
       <c r="Q39" t="n">
         <v>1631.894528442776</v>
@@ -7314,37 +7314,37 @@
         <v>535.8776390590173</v>
       </c>
       <c r="G40" t="n">
-        <v>581.3742049459298</v>
+        <v>581.3742049459025</v>
       </c>
       <c r="H40" t="n">
-        <v>642.9807901053274</v>
+        <v>642.9807901053001</v>
       </c>
       <c r="I40" t="n">
-        <v>756.2036690414103</v>
+        <v>756.203669041383</v>
       </c>
       <c r="J40" t="n">
-        <v>1009.377409693862</v>
+        <v>1009.377409693834</v>
       </c>
       <c r="K40" t="n">
-        <v>1011.83184363073</v>
+        <v>1011.831843630703</v>
       </c>
       <c r="L40" t="n">
-        <v>1011.83184363073</v>
+        <v>1011.831843630703</v>
       </c>
       <c r="M40" t="n">
-        <v>784.0868097952352</v>
+        <v>1011.831843630703</v>
       </c>
       <c r="N40" t="n">
-        <v>501.0715822480788</v>
+        <v>1011.831843630703</v>
       </c>
       <c r="O40" t="n">
-        <v>501.0715822480788</v>
+        <v>1011.831843630703</v>
       </c>
       <c r="P40" t="n">
-        <v>501.0715822480788</v>
+        <v>941.0737317239891</v>
       </c>
       <c r="Q40" t="n">
-        <v>61.84</v>
+        <v>501.8421494759102</v>
       </c>
       <c r="R40" t="n">
         <v>61.84</v>
@@ -7378,22 +7378,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>845.2760936952099</v>
+        <v>1079.844065237112</v>
       </c>
       <c r="C41" t="n">
-        <v>845.2760936952099</v>
+        <v>840.9808548906531</v>
       </c>
       <c r="D41" t="n">
-        <v>645.943613149907</v>
+        <v>641.6483743453502</v>
       </c>
       <c r="E41" t="n">
-        <v>452.6473610217569</v>
+        <v>448.3521222172001</v>
       </c>
       <c r="F41" t="n">
-        <v>258.8194532358863</v>
+        <v>254.5242144313295</v>
       </c>
       <c r="G41" t="n">
-        <v>258.8194532358863</v>
+        <v>61.84</v>
       </c>
       <c r="H41" t="n">
         <v>61.84</v>
@@ -7405,49 +7405,49 @@
         <v>453.1491130376558</v>
       </c>
       <c r="K41" t="n">
-        <v>1162.855479385524</v>
+        <v>453.1491130376558</v>
       </c>
       <c r="L41" t="n">
-        <v>1928.125479385524</v>
+        <v>453.1491130376558</v>
       </c>
       <c r="M41" t="n">
-        <v>1928.125479385524</v>
+        <v>963.9979417665908</v>
       </c>
       <c r="N41" t="n">
-        <v>1928.125479385524</v>
+        <v>1577.218261541354</v>
       </c>
       <c r="O41" t="n">
-        <v>1928.125479385524</v>
+        <v>2342.488261541416</v>
       </c>
       <c r="P41" t="n">
-        <v>2653.400904947332</v>
+        <v>3092</v>
       </c>
       <c r="Q41" t="n">
         <v>3092</v>
       </c>
       <c r="R41" t="n">
-        <v>3053.738789062329</v>
+        <v>3092</v>
       </c>
       <c r="S41" t="n">
-        <v>3029.618175488527</v>
+        <v>3092</v>
       </c>
       <c r="T41" t="n">
-        <v>2652.168092934422</v>
+        <v>2754.316418931101</v>
       </c>
       <c r="U41" t="n">
-        <v>2652.168092934422</v>
+        <v>2313.688846659777</v>
       </c>
       <c r="V41" t="n">
-        <v>2231.106452361873</v>
+        <v>1892.627206087228</v>
       </c>
       <c r="W41" t="n">
-        <v>1801.43627460334</v>
+        <v>1462.957028328695</v>
       </c>
       <c r="X41" t="n">
-        <v>1418.323311511756</v>
+        <v>1079.844065237112</v>
       </c>
       <c r="Y41" t="n">
-        <v>1116.992571428113</v>
+        <v>1079.844065237112</v>
       </c>
     </row>
     <row r="42">
@@ -7487,43 +7487,43 @@
         <v>796.7293362696823</v>
       </c>
       <c r="L42" t="n">
-        <v>1278.949797864882</v>
+        <v>1206.770380316046</v>
       </c>
       <c r="M42" t="n">
-        <v>1575.900339607742</v>
+        <v>1503.720922058905</v>
       </c>
       <c r="N42" t="n">
-        <v>1920.05062421531</v>
+        <v>1847.871206666473</v>
       </c>
       <c r="O42" t="n">
-        <v>2369.963075899029</v>
+        <v>2297.783658350192</v>
       </c>
       <c r="P42" t="n">
-        <v>2492.008087641312</v>
+        <v>2621.183002819699</v>
       </c>
       <c r="Q42" t="n">
-        <v>2531.529615201737</v>
+        <v>2660.704530380124</v>
       </c>
       <c r="R42" t="n">
-        <v>2291.956342415337</v>
+        <v>2323.054230084791</v>
       </c>
       <c r="S42" t="n">
-        <v>2035.83108992583</v>
+        <v>2224.105224033037</v>
       </c>
       <c r="T42" t="n">
-        <v>1841.530316978847</v>
+        <v>2029.804451086053</v>
       </c>
       <c r="U42" t="n">
-        <v>1652.428943483709</v>
+        <v>1840.703077590915</v>
       </c>
       <c r="V42" t="n">
-        <v>1448.882815007426</v>
+        <v>1637.156949114632</v>
       </c>
       <c r="W42" t="n">
-        <v>1227.293781765174</v>
+        <v>1415.567915872381</v>
       </c>
       <c r="X42" t="n">
-        <v>1018.341519699126</v>
+        <v>1206.615653806333</v>
       </c>
       <c r="Y42" t="n">
         <v>1018.341519699126</v>
@@ -7536,76 +7536,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>126.3903759570681</v>
+        <v>110.1379787304532</v>
       </c>
       <c r="C43" t="n">
-        <v>126.3903759570681</v>
+        <v>110.1379787304532</v>
       </c>
       <c r="D43" t="n">
-        <v>126.3903759570681</v>
+        <v>110.1379787304532</v>
       </c>
       <c r="E43" t="n">
-        <v>126.3903759570681</v>
+        <v>110.1379787304532</v>
       </c>
       <c r="F43" t="n">
-        <v>126.3903759570681</v>
+        <v>110.1379787304532</v>
       </c>
       <c r="G43" t="n">
-        <v>126.3903759570681</v>
+        <v>77.77043040567538</v>
       </c>
       <c r="H43" t="n">
-        <v>110.4599455513927</v>
+        <v>61.84</v>
       </c>
       <c r="I43" t="n">
-        <v>146.4628244874756</v>
+        <v>61.84</v>
       </c>
       <c r="J43" t="n">
-        <v>322.4165651399269</v>
+        <v>123.6458674564226</v>
       </c>
       <c r="K43" t="n">
-        <v>322.4165651399269</v>
+        <v>123.6458674564226</v>
       </c>
       <c r="L43" t="n">
-        <v>322.4165651399269</v>
+        <v>123.6458674564226</v>
       </c>
       <c r="M43" t="n">
-        <v>322.4165651399269</v>
+        <v>123.6458674564226</v>
       </c>
       <c r="N43" t="n">
-        <v>322.4165651399269</v>
+        <v>123.6458674564226</v>
       </c>
       <c r="O43" t="n">
-        <v>61.84</v>
+        <v>123.6458674564226</v>
       </c>
       <c r="P43" t="n">
-        <v>61.84</v>
+        <v>123.6458674564226</v>
       </c>
       <c r="Q43" t="n">
-        <v>61.84</v>
+        <v>123.6458674564226</v>
       </c>
       <c r="R43" t="n">
-        <v>61.84</v>
+        <v>123.6458674564226</v>
       </c>
       <c r="S43" t="n">
-        <v>61.84</v>
+        <v>123.6458674564226</v>
       </c>
       <c r="T43" t="n">
-        <v>64.78567915880487</v>
+        <v>123.6458674564226</v>
       </c>
       <c r="U43" t="n">
-        <v>126.2068717970915</v>
+        <v>123.6458674564226</v>
       </c>
       <c r="V43" t="n">
-        <v>139.8982646830375</v>
+        <v>123.6458674564226</v>
       </c>
       <c r="W43" t="n">
-        <v>126.3903759570681</v>
+        <v>110.1379787304532</v>
       </c>
       <c r="X43" t="n">
-        <v>126.3903759570681</v>
+        <v>110.1379787304532</v>
       </c>
       <c r="Y43" t="n">
-        <v>126.3903759570681</v>
+        <v>110.1379787304532</v>
       </c>
     </row>
     <row r="44">
@@ -7615,13 +7615,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1014.498037259975</v>
+        <v>609.4021924540671</v>
       </c>
       <c r="C44" t="n">
-        <v>749.3722006508905</v>
+        <v>504.0289201924683</v>
       </c>
       <c r="D44" t="n">
-        <v>723.5877985832448</v>
+        <v>504.0289201924683</v>
       </c>
       <c r="E44" t="n">
         <v>504.0289201924683</v>
@@ -7642,19 +7642,19 @@
         <v>453.1491130376558</v>
       </c>
       <c r="K44" t="n">
-        <v>509.6405851724916</v>
+        <v>453.1491130376558</v>
       </c>
       <c r="L44" t="n">
-        <v>1274.910585172492</v>
+        <v>453.1491130376558</v>
       </c>
       <c r="M44" t="n">
-        <v>1274.910585172492</v>
+        <v>963.9979417665908</v>
       </c>
       <c r="N44" t="n">
-        <v>1888.130904947255</v>
+        <v>1577.218261541354</v>
       </c>
       <c r="O44" t="n">
-        <v>1888.130904947255</v>
+        <v>2342.488261541431</v>
       </c>
       <c r="P44" t="n">
         <v>2653.400904947332</v>
@@ -7663,28 +7663,28 @@
         <v>3092</v>
       </c>
       <c r="R44" t="n">
-        <v>3092</v>
+        <v>3027.476162799703</v>
       </c>
       <c r="S44" t="n">
-        <v>3092</v>
+        <v>2716.518417544831</v>
       </c>
       <c r="T44" t="n">
-        <v>3092</v>
+        <v>2716.518417544831</v>
       </c>
       <c r="U44" t="n">
-        <v>2625.10980146605</v>
+        <v>2249.628219010881</v>
       </c>
       <c r="V44" t="n">
-        <v>2177.785534630874</v>
+        <v>1802.303952175705</v>
       </c>
       <c r="W44" t="n">
-        <v>1721.852730609715</v>
+        <v>1346.371148154546</v>
       </c>
       <c r="X44" t="n">
-        <v>1312.477141255505</v>
+        <v>936.9955588003362</v>
       </c>
       <c r="Y44" t="n">
-        <v>1312.477141255505</v>
+        <v>609.4021924540671</v>
       </c>
     </row>
     <row r="45">
@@ -7694,22 +7694,22 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>719.6927007794795</v>
+        <v>1028.890452379605</v>
       </c>
       <c r="C45" t="n">
-        <v>543.834203359763</v>
+        <v>853.031954959888</v>
       </c>
       <c r="D45" t="n">
-        <v>543.834203359763</v>
+        <v>690.4686348611986</v>
       </c>
       <c r="E45" t="n">
-        <v>386.5896607113664</v>
+        <v>533.2240922128019</v>
       </c>
       <c r="F45" t="n">
-        <v>232.4116381478544</v>
+        <v>379.04606964929</v>
       </c>
       <c r="G45" t="n">
-        <v>92.27069281954398</v>
+        <v>238.9051243209795</v>
       </c>
       <c r="H45" t="n">
         <v>92.27069281954398</v>
@@ -7718,52 +7718,52 @@
         <v>61.84</v>
       </c>
       <c r="J45" t="n">
-        <v>185.796520175299</v>
+        <v>370.9265201752989</v>
       </c>
       <c r="K45" t="n">
-        <v>560.1193362696824</v>
+        <v>578.9400186606695</v>
       </c>
       <c r="L45" t="n">
-        <v>1016.599797864882</v>
+        <v>1035.42048025587</v>
       </c>
       <c r="M45" t="n">
-        <v>1287.810339607742</v>
+        <v>1306.631021998729</v>
       </c>
       <c r="N45" t="n">
-        <v>1606.22062421531</v>
+        <v>1625.041306606297</v>
       </c>
       <c r="O45" t="n">
-        <v>2030.393075899029</v>
+        <v>2049.213758290016</v>
       </c>
       <c r="P45" t="n">
-        <v>2302.357710282822</v>
+        <v>2346.873102759523</v>
       </c>
       <c r="Q45" t="n">
-        <v>2316.139237843247</v>
+        <v>2360.654630319948</v>
       </c>
       <c r="R45" t="n">
-        <v>2316.139237843247</v>
+        <v>2360.654630319948</v>
       </c>
       <c r="S45" t="n">
-        <v>2033.751359091114</v>
+        <v>2360.654630319948</v>
       </c>
       <c r="T45" t="n">
-        <v>1813.187959881504</v>
+        <v>2140.091231110338</v>
       </c>
       <c r="U45" t="n">
-        <v>1597.82396012374</v>
+        <v>1924.727231352574</v>
       </c>
       <c r="V45" t="n">
-        <v>1368.015205384831</v>
+        <v>1694.918476613664</v>
       </c>
       <c r="W45" t="n">
-        <v>1368.015205384831</v>
+        <v>1678.194178498644</v>
       </c>
       <c r="X45" t="n">
-        <v>1132.800317056156</v>
+        <v>1442.979290169969</v>
       </c>
       <c r="Y45" t="n">
-        <v>918.2635566863238</v>
+        <v>1228.442529800137</v>
       </c>
     </row>
     <row r="46">
@@ -7773,76 +7773,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>85.22794999564401</v>
+        <v>104.0330566683016</v>
       </c>
       <c r="C46" t="n">
-        <v>85.22794999564401</v>
+        <v>104.0330566683016</v>
       </c>
       <c r="D46" t="n">
-        <v>85.22794999564401</v>
+        <v>104.0330566683016</v>
       </c>
       <c r="E46" t="n">
-        <v>85.22794999564401</v>
+        <v>104.0330566683016</v>
       </c>
       <c r="F46" t="n">
-        <v>85.22794999564401</v>
+        <v>104.0330566683016</v>
       </c>
       <c r="G46" t="n">
-        <v>85.22794999564401</v>
+        <v>104.0330566683016</v>
       </c>
       <c r="H46" t="n">
-        <v>85.22794999564401</v>
+        <v>61.84</v>
       </c>
       <c r="I46" t="n">
-        <v>95.49082893172692</v>
+        <v>72.10287893608292</v>
       </c>
       <c r="J46" t="n">
-        <v>245.7045695841782</v>
+        <v>143.672759546362</v>
       </c>
       <c r="K46" t="n">
-        <v>245.7045695841782</v>
+        <v>143.672759546362</v>
       </c>
       <c r="L46" t="n">
-        <v>245.7045695841782</v>
+        <v>143.672759546362</v>
       </c>
       <c r="M46" t="n">
-        <v>245.7045695841782</v>
+        <v>143.672759546362</v>
       </c>
       <c r="N46" t="n">
-        <v>245.7045695841782</v>
+        <v>143.672759546362</v>
       </c>
       <c r="O46" t="n">
-        <v>85.09713788510881</v>
+        <v>143.672759546362</v>
       </c>
       <c r="P46" t="n">
-        <v>85.09713788510881</v>
+        <v>143.672759546362</v>
       </c>
       <c r="Q46" t="n">
-        <v>85.09713788510881</v>
+        <v>143.672759546362</v>
       </c>
       <c r="R46" t="n">
-        <v>85.09713788510881</v>
+        <v>143.672759546362</v>
       </c>
       <c r="S46" t="n">
-        <v>85.09713788510881</v>
+        <v>143.672759546362</v>
       </c>
       <c r="T46" t="n">
-        <v>61.84</v>
+        <v>120.4156216612533</v>
       </c>
       <c r="U46" t="n">
-        <v>97.52119263828664</v>
+        <v>156.0968142995399</v>
       </c>
       <c r="V46" t="n">
-        <v>85.22794999564401</v>
+        <v>143.8035716568973</v>
       </c>
       <c r="W46" t="n">
-        <v>85.22794999564401</v>
+        <v>104.0330566683016</v>
       </c>
       <c r="X46" t="n">
-        <v>85.22794999564401</v>
+        <v>104.0330566683016</v>
       </c>
       <c r="Y46" t="n">
-        <v>85.22794999564401</v>
+        <v>104.0330566683016</v>
       </c>
     </row>
   </sheetData>
@@ -7964,25 +7964,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>51.24160624509022</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K2" t="n">
-        <v>716.8751175230994</v>
+        <v>500.8454983898772</v>
       </c>
       <c r="L2" t="n">
-        <v>782.4479756267968</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N2" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O2" t="n">
-        <v>70.24786957409242</v>
+        <v>884.2478695740924</v>
       </c>
       <c r="P2" t="n">
-        <v>814.2870600406815</v>
+        <v>0.2870600406814674</v>
       </c>
       <c r="Q2" t="n">
         <v>615.8520732695737</v>
@@ -8201,19 +8201,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>51.24160624509045</v>
+        <v>51.24160624509022</v>
       </c>
       <c r="K5" t="n">
-        <v>716.8751175230994</v>
+        <v>685.3230931498963</v>
       </c>
       <c r="L5" t="n">
-        <v>163.0335112078445</v>
+        <v>814</v>
       </c>
       <c r="M5" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N5" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O5" t="n">
         <v>70.24786957409242</v>
@@ -8441,22 +8441,22 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K8" t="n">
-        <v>716.8751175230994</v>
+        <v>202.8544162978881</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N8" t="n">
         <v>1096.663422488788</v>
       </c>
       <c r="O8" t="n">
-        <v>668.2182504408704</v>
+        <v>884.247869574097</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2870600406814674</v>
+        <v>814.2870600406815</v>
       </c>
       <c r="Q8" t="n">
         <v>615.8520732695737</v>
@@ -8675,28 +8675,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K11" t="n">
-        <v>161.6966466921584</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L11" t="n">
-        <v>814</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N11" t="n">
         <v>1096.663422488788</v>
       </c>
       <c r="O11" t="n">
-        <v>884.2478695740924</v>
+        <v>602.7693615519817</v>
       </c>
       <c r="P11" t="n">
-        <v>814.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q11" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8924,13 +8924,13 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N14" t="n">
-        <v>839.4760337498315</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O14" t="n">
         <v>884.2478695740924</v>
       </c>
       <c r="P14" t="n">
-        <v>814.2870600406815</v>
+        <v>557.0996713017253</v>
       </c>
       <c r="Q14" t="n">
         <v>172.8226843274854</v>
@@ -9152,10 +9152,10 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
-        <v>435.3966095009885</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L17" t="n">
-        <v>814</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>1060.271045550332</v>
@@ -9164,7 +9164,7 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O17" t="n">
-        <v>70.24786957409245</v>
+        <v>602.7693615519817</v>
       </c>
       <c r="P17" t="n">
         <v>0.2870600406814136</v>
@@ -9389,16 +9389,16 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
-        <v>716.8751175230994</v>
+        <v>240.811073919941</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="M20" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N20" t="n">
-        <v>815.1849144666769</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O20" t="n">
         <v>70.24786957409245</v>
@@ -9629,22 +9629,22 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L23" t="n">
-        <v>482.9742632469452</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N23" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O23" t="n">
-        <v>884.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P23" t="n">
-        <v>814.2870600406815</v>
+        <v>532.8085520185707</v>
       </c>
       <c r="Q23" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9860,13 +9860,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K26" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>772.9999999999999</v>
+        <v>676.4765574844688</v>
       </c>
       <c r="M26" t="n">
         <v>544.2621276423173</v>
@@ -9875,10 +9875,10 @@
         <v>477.2489580698352</v>
       </c>
       <c r="O26" t="n">
-        <v>843.2478695741199</v>
+        <v>843.247869574119</v>
       </c>
       <c r="P26" t="n">
-        <v>355.1502303431427</v>
+        <v>773.2870600407081</v>
       </c>
       <c r="Q26" t="n">
         <v>615.8520732695737</v>
@@ -10109,16 +10109,16 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N29" t="n">
-        <v>693.8414801232076</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O29" t="n">
-        <v>843.2478695741272</v>
+        <v>843.2478695741263</v>
       </c>
       <c r="P29" t="n">
-        <v>0.2870600406814136</v>
+        <v>40.49450661719048</v>
       </c>
       <c r="Q29" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10337,10 +10337,10 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L32" t="n">
-        <v>221.70671065707</v>
+        <v>705.4782820760967</v>
       </c>
       <c r="M32" t="n">
         <v>1060.271045550332</v>
@@ -10349,13 +10349,13 @@
         <v>477.2489580698352</v>
       </c>
       <c r="O32" t="n">
-        <v>843.2478695741345</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P32" t="n">
-        <v>773.2870600407235</v>
+        <v>773.2870600407226</v>
       </c>
       <c r="Q32" t="n">
-        <v>615.8520732695737</v>
+        <v>188.2053843274865</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10571,25 +10571,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J35" t="n">
-        <v>430.3047365861567</v>
+        <v>50.42570624509119</v>
       </c>
       <c r="K35" t="n">
-        <v>716.8751175230994</v>
+        <v>29.8521478483128</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1060.271045550332</v>
+        <v>1012.590174281184</v>
       </c>
       <c r="N35" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O35" t="n">
-        <v>843.2478695741418</v>
+        <v>843.2478695741409</v>
       </c>
       <c r="P35" t="n">
-        <v>278.1186531746876</v>
+        <v>773.2870600407299</v>
       </c>
       <c r="Q35" t="n">
         <v>615.8520732695737</v>
@@ -10814,22 +10814,22 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>649.3533995991291</v>
+        <v>375.292246238141</v>
       </c>
       <c r="M38" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N38" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O38" t="n">
-        <v>843.247869574149</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P38" t="n">
-        <v>773.2870600407381</v>
+        <v>773.2870600407372</v>
       </c>
       <c r="Q38" t="n">
-        <v>188.2053843274866</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -11048,25 +11048,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K41" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>773</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N41" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O41" t="n">
-        <v>70.24786957409245</v>
+        <v>843.2478695741554</v>
       </c>
       <c r="P41" t="n">
-        <v>732.888500002104</v>
+        <v>757.3696241402611</v>
       </c>
       <c r="Q41" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11285,22 +11285,22 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K44" t="n">
-        <v>57.06209306549079</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>773</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N44" t="n">
         <v>1096.663422488788</v>
       </c>
       <c r="O44" t="n">
-        <v>70.24786957409245</v>
+        <v>843.24786957417</v>
       </c>
       <c r="P44" t="n">
-        <v>773.2870600407599</v>
+        <v>314.3402351981579</v>
       </c>
       <c r="Q44" t="n">
         <v>615.8520732695737</v>
@@ -22709,7 +22709,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>29.21007785422381</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -22718,7 +22718,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>29.2100778542287</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -22940,7 +22940,7 @@
         <v>23.54762815777917</v>
       </c>
       <c r="M7" t="n">
-        <v>5.662449696445705</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -22955,7 +22955,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>5.662449696449244</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -23174,10 +23174,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>23.54762815777917</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>5.662449696449983</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -23192,7 +23192,7 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>29.21007785422461</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -23241,7 +23241,7 @@
         <v>178.7573722870162</v>
       </c>
       <c r="H11" t="n">
-        <v>183.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -23271,10 +23271,10 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>25.87859882829446</v>
       </c>
       <c r="S11" t="n">
-        <v>241.178886845468</v>
+        <v>111.9925140378948</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -23292,7 +23292,7 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>286.3174326828064</v>
       </c>
     </row>
     <row r="12">
@@ -23384,7 +23384,7 @@
         <v>62.11380033707866</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>47.72524664804467</v>
       </c>
       <c r="D13" t="n">
         <v>60.53621805555548</v>
@@ -23399,7 +23399,7 @@
         <v>20.04387284153003</v>
       </c>
       <c r="H13" t="n">
-        <v>3.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -23420,7 +23420,7 @@
         <v>346.1850752716849</v>
       </c>
       <c r="O13" t="n">
-        <v>415.445564079015</v>
+        <v>74.66876459048729</v>
       </c>
       <c r="P13" t="n">
         <v>462.4478973282775</v>
@@ -23429,7 +23429,7 @@
         <v>500.839266425598</v>
       </c>
       <c r="R13" t="n">
-        <v>203.4066392003398</v>
+        <v>501.6021279811511</v>
       </c>
       <c r="S13" t="n">
         <v>137.3734797028554</v>
@@ -23444,7 +23444,7 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
         <v>22.44364543010755</v>
@@ -23460,10 +23460,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>81.53132120304619</v>
+        <v>230.9993129555745</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>161.431295659011</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -23472,13 +23472,13 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>153.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>157.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -23660,16 +23660,16 @@
         <v>389.445564079015</v>
       </c>
       <c r="P16" t="n">
-        <v>436.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>474.839266425598</v>
+        <v>382.7066165981674</v>
       </c>
       <c r="R16" t="n">
-        <v>58.39506052829842</v>
+        <v>475.6021279811511</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>111.3734797028554</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -23864,7 +23864,7 @@
         <v>6.53621805555548</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>1.98090483695654</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -23891,7 +23891,7 @@
         <v>241.6316114025499</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>292.1850752716849</v>
       </c>
       <c r="O19" t="n">
         <v>361.445564079015</v>
@@ -23900,13 +23900,13 @@
         <v>408.4478973282775</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>108.2004986247733</v>
       </c>
       <c r="R19" t="n">
-        <v>447.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>38.1378304551199</v>
+        <v>83.37347970285543</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -23940,7 +23940,7 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4306086145859638</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -23994,7 +23994,7 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.4306086145317636</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
@@ -24134,16 +24134,16 @@
         <v>361.445564079015</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>408.4478973282775</v>
       </c>
       <c r="Q22" t="n">
-        <v>77.51162082136199</v>
+        <v>191.5739783276288</v>
       </c>
       <c r="R22" t="n">
-        <v>447.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>83.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -24161,7 +24161,7 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>8.465352849462363</v>
       </c>
     </row>
     <row r="23">
@@ -24189,7 +24189,7 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4306086145176096</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -24234,7 +24234,7 @@
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.4306086145857648</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -24329,13 +24329,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2534801416616297</v>
+        <v>8.113800337078658</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>6.53621805555548</v>
       </c>
       <c r="E25" t="n">
         <v>1.98090483695654</v>
@@ -24362,25 +24362,25 @@
         <v>144.5476281577792</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>241.6316114025499</v>
       </c>
       <c r="N25" t="n">
         <v>292.1850752716849</v>
       </c>
       <c r="O25" t="n">
-        <v>361.445564079015</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>408.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>446.839266425598</v>
       </c>
       <c r="R25" t="n">
-        <v>447.6021279811511</v>
+        <v>431.2546936064678</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>83.37347970285543</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -24414,16 +24414,16 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>142.1601174688974</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>179.3632896068686</v>
       </c>
       <c r="F26" t="n">
         <v>179.8896287080119</v>
       </c>
       <c r="G26" t="n">
-        <v>178.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>183.0096587035274</v>
@@ -24468,7 +24468,7 @@
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>142.7660347887499</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
@@ -24578,7 +24578,7 @@
         <v>55.98090483695654</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>49.38285596774193</v>
       </c>
       <c r="G28" t="n">
         <v>20.04387284153003</v>
@@ -24605,7 +24605,7 @@
         <v>346.1850752716849</v>
       </c>
       <c r="O28" t="n">
-        <v>122.6788107195195</v>
+        <v>415.445564079015</v>
       </c>
       <c r="P28" t="n">
         <v>462.4478973282775</v>
@@ -24614,7 +24614,7 @@
         <v>500.839266425598</v>
       </c>
       <c r="R28" t="n">
-        <v>501.6021279811511</v>
+        <v>160.8253284926234</v>
       </c>
       <c r="S28" t="n">
         <v>137.3734797028554</v>
@@ -24629,7 +24629,7 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
         <v>22.44364543010755</v>
@@ -24654,16 +24654,16 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>179.3632896068686</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>179.8896287080119</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>178.7573722870162</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>146.4124038854086</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -24693,10 +24693,10 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>9.723502518158682</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>269.8481678023229</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
         <v>0</v>
@@ -24705,7 +24705,7 @@
         <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>404.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
         <v>0</v>
@@ -24818,7 +24818,7 @@
         <v>49.38285596774193</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>20.04387284153003</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -24830,7 +24830,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>63.52077380114304</v>
       </c>
       <c r="L31" t="n">
         <v>198.5476281577792</v>
@@ -24845,13 +24845,13 @@
         <v>415.445564079015</v>
       </c>
       <c r="P31" t="n">
-        <v>462.4478973282775</v>
+        <v>121.6710978397498</v>
       </c>
       <c r="Q31" t="n">
         <v>500.839266425598</v>
       </c>
       <c r="R31" t="n">
-        <v>306.8553279847588</v>
+        <v>501.6021279811511</v>
       </c>
       <c r="S31" t="n">
         <v>137.3734797028554</v>
@@ -24872,7 +24872,7 @@
         <v>22.44364543010755</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>62.46535284946236</v>
       </c>
     </row>
     <row r="32">
@@ -25070,25 +25070,25 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>132.5476281577792</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>229.6316114025499</v>
       </c>
       <c r="N34" t="n">
         <v>280.1850752716849</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>349.445564079015</v>
       </c>
       <c r="P34" t="n">
-        <v>396.4478973282775</v>
+        <v>326.3973665406309</v>
       </c>
       <c r="Q34" t="n">
-        <v>434.839266425598</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>206.7350064260758</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>71.37347970285543</v>
@@ -25307,16 +25307,16 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>132.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>4.926889460966834</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>349.445564079015</v>
+        <v>51.3179537166331</v>
       </c>
       <c r="P37" t="n">
         <v>396.4478973282775</v>
@@ -25325,7 +25325,7 @@
         <v>434.839266425598</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>435.6021279811511</v>
       </c>
       <c r="S37" t="n">
         <v>71.37347970285543</v>
@@ -25547,22 +25547,22 @@
         <v>132.5476281577792</v>
       </c>
       <c r="M40" t="n">
-        <v>4.164027905409995</v>
+        <v>229.6316114025499</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>280.1850752716849</v>
       </c>
       <c r="O40" t="n">
         <v>349.445564079015</v>
       </c>
       <c r="P40" t="n">
-        <v>396.4478973282775</v>
+        <v>326.3973665406309</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>435.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>71.37347970285543</v>
@@ -25593,10 +25593,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>268.9993129555745</v>
       </c>
       <c r="C41" t="n">
-        <v>236.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -25608,10 +25608,10 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>190.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>195.0096587035274</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -25641,16 +25641,16 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>37.87859882829446</v>
       </c>
       <c r="S41" t="n">
-        <v>257.9687603642593</v>
+        <v>281.8481678023229</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>39.36883647035432</v>
       </c>
       <c r="U41" t="n">
-        <v>436.2212965486107</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -25662,7 +25662,7 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>298.3174326828064</v>
       </c>
     </row>
     <row r="42">
@@ -25720,10 +25720,10 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>97.09625723384272</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>155.6044839733747</v>
       </c>
       <c r="T42" t="n">
         <v>0</v>
@@ -25741,7 +25741,7 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>186.3913927661343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -25766,7 +25766,7 @@
         <v>61.38285596774193</v>
       </c>
       <c r="G43" t="n">
-        <v>32.04387284153003</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -25790,7 +25790,7 @@
         <v>358.1850752716849</v>
       </c>
       <c r="O43" t="n">
-        <v>169.4747645904874</v>
+        <v>427.445564079015</v>
       </c>
       <c r="P43" t="n">
         <v>474.4478973282775</v>
@@ -25830,16 +25830,16 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>294.9993129555745</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>158.1550387040112</v>
       </c>
       <c r="D44" t="n">
-        <v>197.8125976928805</v>
+        <v>223.3391557398498</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>217.3632896068686</v>
       </c>
       <c r="F44" t="n">
         <v>217.8896287080119</v>
@@ -25878,10 +25878,10 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>63.87859882829446</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>307.8481678023229</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
         <v>399.6755817285639</v>
@@ -25899,7 +25899,7 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>324.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -25909,13 +25909,13 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.9714092985508103</v>
+        <v>0</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>160.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
@@ -25927,7 +25927,7 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>145.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -25960,7 +25960,7 @@
         <v>360.2737972923793</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>279.5639999646113</v>
       </c>
       <c r="T45" t="n">
         <v>0</v>
@@ -25972,7 +25972,7 @@
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>245.3731429098285</v>
+        <v>228.816087775958</v>
       </c>
       <c r="X45" t="n">
         <v>0</v>
@@ -26006,7 +26006,7 @@
         <v>58.04387284153003</v>
       </c>
       <c r="H46" t="n">
-        <v>41.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
@@ -26027,7 +26027,7 @@
         <v>384.1850752716849</v>
       </c>
       <c r="O46" t="n">
-        <v>294.4442066969362</v>
+        <v>453.445564079015</v>
       </c>
       <c r="P46" t="n">
         <v>500.4478973282775</v>
@@ -26051,7 +26051,7 @@
         <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>39.37280983870968</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
         <v>60.44364543010755</v>
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>3327197.162247744</v>
+        <v>3327197.162247743</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>3967254.058352318</v>
+        <v>3967254.058352316</v>
       </c>
     </row>
     <row r="8">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5247367.850561465</v>
+        <v>5247367.850561461</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5828330.065894746</v>
+        <v>5828330.065894741</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6412845.979005806</v>
+        <v>6412845.9790058</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7057850.731309424</v>
+        <v>7057850.731309419</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>7701514.960347092</v>
+        <v>7701514.960347085</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>8345179.189384759</v>
+        <v>8345179.189384755</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>8910908.188540872</v>
+        <v>8910908.188540868</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>9439834.178497549</v>
+        <v>9439834.178497545</v>
       </c>
     </row>
   </sheetData>
@@ -26269,7 +26269,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1541878.098118515</v>
+        <v>1541878.098118514</v>
       </c>
       <c r="C2" t="n">
         <v>1541878.098118515</v>
@@ -26284,34 +26284,34 @@
         <v>1435639.178444159</v>
       </c>
       <c r="G2" t="n">
+        <v>1493466.090910675</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1493466.090910679</v>
+      </c>
+      <c r="I2" t="n">
         <v>1493466.090910674</v>
       </c>
-      <c r="H2" t="n">
-        <v>1493466.090910675</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1493466.090910681</v>
-      </c>
       <c r="J2" t="n">
-        <v>1363870.46392581</v>
+        <v>1363870.463925811</v>
       </c>
       <c r="K2" t="n">
         <v>1363870.46392581</v>
       </c>
       <c r="L2" t="n">
-        <v>1501883.201087888</v>
+        <v>1501883.201087886</v>
       </c>
       <c r="M2" t="n">
-        <v>1501883.201087888</v>
+        <v>1501883.201087886</v>
       </c>
       <c r="N2" t="n">
         <v>1501883.201087887</v>
       </c>
       <c r="O2" t="n">
-        <v>1323162.21898481</v>
+        <v>1323162.218984811</v>
       </c>
       <c r="P2" t="n">
-        <v>1234160.643232238</v>
+        <v>1234160.643232237</v>
       </c>
     </row>
     <row r="3">
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>575615.820517953</v>
+        <v>580502.3723909451</v>
       </c>
       <c r="C4" t="n">
-        <v>573863.9117786936</v>
+        <v>578750.4636516855</v>
       </c>
       <c r="D4" t="n">
-        <v>572109.6264658828</v>
+        <v>576996.1783388748</v>
       </c>
       <c r="E4" t="n">
-        <v>493887.8206072089</v>
+        <v>498724.2862854869</v>
       </c>
       <c r="F4" t="n">
-        <v>518162.4364012046</v>
+        <v>522998.9020794827</v>
       </c>
       <c r="G4" t="n">
-        <v>542951.8445255277</v>
+        <v>547788.3102038058</v>
       </c>
       <c r="H4" t="n">
-        <v>541278.9095854306</v>
+        <v>546115.375263711</v>
       </c>
       <c r="I4" t="n">
-        <v>539603.639201007</v>
+        <v>544440.1048792817</v>
       </c>
       <c r="J4" t="n">
-        <v>483069.4589672089</v>
+        <v>487781.687779115</v>
       </c>
       <c r="K4" t="n">
-        <v>481604.7173132672</v>
+        <v>486316.9461251733</v>
       </c>
       <c r="L4" t="n">
-        <v>543419.7365500293</v>
+        <v>548178.8299014302</v>
       </c>
       <c r="M4" t="n">
-        <v>541689.6178484766</v>
+        <v>546448.7111998776</v>
       </c>
       <c r="N4" t="n">
-        <v>539957.0115239245</v>
+        <v>544716.1048753253</v>
       </c>
       <c r="O4" t="n">
-        <v>457615.9305970519</v>
+        <v>462328.1594089579</v>
       </c>
       <c r="P4" t="n">
-        <v>416810.1932019159</v>
+        <v>421522.422013822</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>596615.4776005615</v>
+        <v>591728.9257275693</v>
       </c>
       <c r="C6" t="n">
-        <v>884895.3863398212</v>
+        <v>880008.8344668292</v>
       </c>
       <c r="D6" t="n">
-        <v>886649.6716526318</v>
+        <v>881763.1197796401</v>
       </c>
       <c r="E6" t="n">
-        <v>637091.0074466019</v>
+        <v>632254.5417683239</v>
       </c>
       <c r="F6" t="n">
-        <v>826084.2230429545</v>
+        <v>821247.7573646763</v>
       </c>
       <c r="G6" t="n">
-        <v>855167.7953851466</v>
+        <v>850331.3297068692</v>
       </c>
       <c r="H6" t="n">
-        <v>879240.7303252444</v>
+        <v>874404.2646469685</v>
       </c>
       <c r="I6" t="n">
-        <v>880916.0007096741</v>
+        <v>876079.5350313926</v>
       </c>
       <c r="J6" t="n">
-        <v>405991.0799586012</v>
+        <v>401278.8511466955</v>
       </c>
       <c r="K6" t="n">
-        <v>795551.8216125432</v>
+        <v>790839.592800637</v>
       </c>
       <c r="L6" t="n">
-        <v>811800.9855378587</v>
+        <v>807041.8921864561</v>
       </c>
       <c r="M6" t="n">
-        <v>888731.1042394117</v>
+        <v>883972.0108880089</v>
       </c>
       <c r="N6" t="n">
-        <v>890463.7105639628</v>
+        <v>885704.6172125614</v>
       </c>
       <c r="O6" t="n">
-        <v>726241.1913877586</v>
+        <v>721528.9625758528</v>
       </c>
       <c r="P6" t="n">
-        <v>754631.147030322</v>
+        <v>749918.9182184153</v>
       </c>
     </row>
   </sheetData>
@@ -26990,10 +26990,10 @@
         <v>28</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>171</v>
@@ -27054,13 +27054,13 @@
         <v>-0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>-0</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O3" t="n">
         <v>-0</v>
@@ -27433,10 +27433,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="C2" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>400</v>
@@ -27448,10 +27448,10 @@
         <v>400</v>
       </c>
       <c r="G2" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>150.0811596826846</v>
@@ -27481,13 +27481,13 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>306.430608614585</v>
       </c>
       <c r="T2" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
         <v>400</v>
@@ -27496,13 +27496,13 @@
         <v>400</v>
       </c>
       <c r="W2" t="n">
-        <v>157.3092074428802</v>
+        <v>400</v>
       </c>
       <c r="X2" t="n">
         <v>400</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
     </row>
     <row r="3">
@@ -27530,10 +27530,10 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H3" t="n">
-        <v>47.52172789347816</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27560,7 +27560,7 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>400</v>
+        <v>264.6481137848265</v>
       </c>
       <c r="S3" t="n">
         <v>400</v>
@@ -27575,7 +27575,7 @@
         <v>400</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="X3" t="n">
         <v>400</v>
@@ -27594,31 +27594,31 @@
         <v>287.1138003370787</v>
       </c>
       <c r="C4" t="n">
-        <v>400</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D4" t="n">
-        <v>400</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E4" t="n">
         <v>280.9809048369565</v>
       </c>
       <c r="F4" t="n">
+        <v>274.3828559677419</v>
+      </c>
+      <c r="G4" t="n">
+        <v>245.04387284153</v>
+      </c>
+      <c r="H4" t="n">
+        <v>385.6123339023288</v>
+      </c>
+      <c r="I4" t="n">
         <v>400</v>
       </c>
-      <c r="G4" t="n">
+      <c r="J4" t="n">
         <v>400</v>
       </c>
-      <c r="H4" t="n">
-        <v>228.7711261016186</v>
-      </c>
-      <c r="I4" t="n">
-        <v>176.6334556201183</v>
-      </c>
-      <c r="J4" t="n">
-        <v>35.26894883590776</v>
-      </c>
       <c r="K4" t="n">
-        <v>395.3238934042286</v>
+        <v>400</v>
       </c>
       <c r="L4" t="n">
         <v>400</v>
@@ -27642,25 +27642,25 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
-        <v>400</v>
+        <v>362.3734797028554</v>
       </c>
       <c r="T4" t="n">
         <v>400</v>
       </c>
       <c r="U4" t="n">
-        <v>150.9583912744579</v>
+        <v>400</v>
       </c>
       <c r="V4" t="n">
         <v>400</v>
       </c>
       <c r="W4" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X4" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y4" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="5">
@@ -27676,16 +27676,16 @@
         <v>400</v>
       </c>
       <c r="D5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>400</v>
       </c>
       <c r="G5" t="n">
-        <v>400</v>
+        <v>56.51176829727012</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -27730,16 +27730,16 @@
         <v>400</v>
       </c>
       <c r="V5" t="n">
-        <v>56.51176829727012</v>
+        <v>400</v>
       </c>
       <c r="W5" t="n">
         <v>400</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
     </row>
     <row r="6">
@@ -27749,13 +27749,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>235.8685316061257</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
         <v>342.6720972219126</v>
@@ -27794,7 +27794,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>400</v>
@@ -27806,7 +27806,7 @@
         <v>400</v>
       </c>
       <c r="U6" t="n">
-        <v>400</v>
+        <v>76.45355315257615</v>
       </c>
       <c r="V6" t="n">
         <v>400</v>
@@ -27831,31 +27831,31 @@
         <v>400</v>
       </c>
       <c r="C7" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D7" t="n">
-        <v>400</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E7" t="n">
         <v>400</v>
       </c>
       <c r="F7" t="n">
+        <v>274.3828559677419</v>
+      </c>
+      <c r="G7" t="n">
         <v>400</v>
-      </c>
-      <c r="G7" t="n">
-        <v>245.04387284153</v>
       </c>
       <c r="H7" t="n">
         <v>400</v>
       </c>
       <c r="I7" t="n">
-        <v>176.6334556201183</v>
+        <v>400</v>
       </c>
       <c r="J7" t="n">
+        <v>35.26894883590776</v>
+      </c>
+      <c r="K7" t="n">
         <v>400</v>
-      </c>
-      <c r="K7" t="n">
-        <v>288.520773801143</v>
       </c>
       <c r="L7" t="n">
         <v>400</v>
@@ -27882,19 +27882,19 @@
         <v>400</v>
       </c>
       <c r="T7" t="n">
+        <v>225.783189055375</v>
+      </c>
+      <c r="U7" t="n">
         <v>400</v>
-      </c>
-      <c r="U7" t="n">
-        <v>150.9583912744579</v>
       </c>
       <c r="V7" t="n">
         <v>199.1703102162162</v>
       </c>
       <c r="W7" t="n">
-        <v>334.5331171593975</v>
+        <v>400</v>
       </c>
       <c r="X7" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y7" t="n">
         <v>287.4653528494624</v>
@@ -27907,7 +27907,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="C8" t="n">
         <v>400</v>
@@ -27919,13 +27919,13 @@
         <v>400</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>157.3092074428802</v>
       </c>
       <c r="I8" t="n">
         <v>150.0811596826846</v>
@@ -27955,16 +27955,16 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>250.8785988282945</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
         <v>400</v>
       </c>
-      <c r="T8" t="n">
-        <v>306.4306086145853</v>
-      </c>
       <c r="U8" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>400</v>
@@ -28007,7 +28007,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -28031,7 +28031,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>400</v>
@@ -28043,10 +28043,10 @@
         <v>400</v>
       </c>
       <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
         <v>400</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>400</v>
@@ -28055,7 +28055,7 @@
         <v>400</v>
       </c>
       <c r="Y9" t="n">
-        <v>158.7921542740601</v>
+        <v>114.7450334731912</v>
       </c>
     </row>
     <row r="10">
@@ -28071,13 +28071,13 @@
         <v>400</v>
       </c>
       <c r="D10" t="n">
+        <v>285.5362180555555</v>
+      </c>
+      <c r="E10" t="n">
         <v>400</v>
       </c>
-      <c r="E10" t="n">
-        <v>280.9809048369565</v>
-      </c>
       <c r="F10" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G10" t="n">
         <v>400</v>
@@ -28086,10 +28086,10 @@
         <v>400</v>
       </c>
       <c r="I10" t="n">
-        <v>176.6334556201183</v>
+        <v>400</v>
       </c>
       <c r="J10" t="n">
-        <v>110.0448310811607</v>
+        <v>35.26894883590776</v>
       </c>
       <c r="K10" t="n">
         <v>400</v>
@@ -28119,19 +28119,19 @@
         <v>400</v>
       </c>
       <c r="T10" t="n">
+        <v>210.0245665062577</v>
+      </c>
+      <c r="U10" t="n">
+        <v>150.9583912744579</v>
+      </c>
+      <c r="V10" t="n">
+        <v>338.3533974586216</v>
+      </c>
+      <c r="W10" t="n">
         <v>400</v>
       </c>
-      <c r="U10" t="n">
-        <v>400</v>
-      </c>
-      <c r="V10" t="n">
-        <v>199.1703102162162</v>
-      </c>
-      <c r="W10" t="n">
-        <v>226.3728098387097</v>
-      </c>
       <c r="X10" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y10" t="n">
         <v>287.4653528494624</v>
@@ -28244,7 +28244,7 @@
         <v>225</v>
       </c>
       <c r="I12" t="n">
-        <v>217.1263858913485</v>
+        <v>225</v>
       </c>
       <c r="J12" t="n">
         <v>225</v>
@@ -28253,13 +28253,13 @@
         <v>225</v>
       </c>
       <c r="L12" t="n">
-        <v>26.99048536749041</v>
+        <v>225</v>
       </c>
       <c r="M12" t="n">
         <v>225</v>
       </c>
       <c r="N12" t="n">
-        <v>225</v>
+        <v>19.1168712588389</v>
       </c>
       <c r="O12" t="n">
         <v>225</v>
@@ -28481,25 +28481,25 @@
         <v>251</v>
       </c>
       <c r="I15" t="n">
-        <v>217.1263858913485</v>
+        <v>251</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
         <v>251</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
       <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>166.1982915220776</v>
+      </c>
+      <c r="O15" t="n">
         <v>251</v>
-      </c>
-      <c r="M15" t="n">
-        <v>200.0719056307287</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
       </c>
       <c r="P15" t="n">
         <v>251</v>
@@ -28724,25 +28724,25 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>217.5442043757546</v>
+      </c>
+      <c r="P18" t="n">
         <v>279</v>
       </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
+      <c r="Q18" t="n">
         <v>279</v>
-      </c>
-      <c r="O18" t="n">
-        <v>44.46493928527505</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>173.0792650904796</v>
       </c>
       <c r="R18" t="n">
         <v>279</v>
@@ -28903,7 +28903,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>250.8785988282945</v>
+        <v>250.8785988283496</v>
       </c>
       <c r="S20" t="n">
         <v>279</v>
@@ -29140,7 +29140,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>250.8785988283643</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S23" t="n">
         <v>279</v>
@@ -29201,22 +29201,22 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>155.670590267103</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
         <v>279</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>261.5913251766237</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>173.0792650904796</v>
       </c>
       <c r="R24" t="n">
         <v>279</v>
@@ -29441,13 +29441,13 @@
         <v>225</v>
       </c>
       <c r="M27" t="n">
-        <v>19.11687125883903</v>
+        <v>225</v>
       </c>
       <c r="N27" t="n">
         <v>225</v>
       </c>
       <c r="O27" t="n">
-        <v>225</v>
+        <v>19.11687125883898</v>
       </c>
       <c r="P27" t="n">
         <v>225</v>
@@ -29681,13 +29681,13 @@
         <v>225</v>
       </c>
       <c r="N30" t="n">
-        <v>225</v>
+        <v>19.11687125883913</v>
       </c>
       <c r="O30" t="n">
         <v>225</v>
       </c>
       <c r="P30" t="n">
-        <v>19.11687125883908</v>
+        <v>225</v>
       </c>
       <c r="Q30" t="n">
         <v>225</v>
@@ -29824,7 +29824,7 @@
         <v>291</v>
       </c>
       <c r="I32" t="n">
-        <v>141.6245682972704</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -29872,7 +29872,7 @@
         <v>291</v>
       </c>
       <c r="Y32" t="n">
-        <v>291</v>
+        <v>282.5434086145857</v>
       </c>
     </row>
     <row r="33">
@@ -29906,28 +29906,28 @@
         <v>217.1263858913485</v>
       </c>
       <c r="J33" t="n">
-        <v>127.8102101760008</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>291</v>
       </c>
       <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>9.889475266480332</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
         <v>291</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>173.0792650904796</v>
       </c>
       <c r="R33" t="n">
         <v>291</v>
@@ -29961,7 +29961,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>291.0000000000239</v>
+        <v>291</v>
       </c>
       <c r="C34" t="n">
         <v>291</v>
@@ -30061,7 +30061,7 @@
         <v>291</v>
       </c>
       <c r="I35" t="n">
-        <v>141.6245682972704</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -30109,7 +30109,7 @@
         <v>291</v>
       </c>
       <c r="Y35" t="n">
-        <v>291</v>
+        <v>282.5434086145857</v>
       </c>
     </row>
     <row r="36">
@@ -30140,16 +30140,16 @@
         <v>291</v>
       </c>
       <c r="I36" t="n">
-        <v>217.1263858913485</v>
+        <v>291</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>227.0158611578289</v>
       </c>
       <c r="L36" t="n">
-        <v>9.88947526648036</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -30161,7 +30161,7 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>291</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
         <v>291</v>
@@ -30198,7 +30198,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>291.0000000000239</v>
+        <v>291</v>
       </c>
       <c r="C37" t="n">
         <v>291</v>
@@ -30292,7 +30292,7 @@
         <v>291</v>
       </c>
       <c r="G38" t="n">
-        <v>282.5434086145858</v>
+        <v>291</v>
       </c>
       <c r="H38" t="n">
         <v>291</v>
@@ -30328,7 +30328,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S38" t="n">
-        <v>291</v>
+        <v>282.5434086145851</v>
       </c>
       <c r="T38" t="n">
         <v>291</v>
@@ -30395,13 +30395,13 @@
         <v>0</v>
       </c>
       <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>227.0158611578287</v>
+      </c>
+      <c r="Q39" t="n">
         <v>291</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>227.0158611578287</v>
       </c>
       <c r="R39" t="n">
         <v>291</v>
@@ -30450,7 +30450,7 @@
         <v>291</v>
       </c>
       <c r="G40" t="n">
-        <v>291.0000000000276</v>
+        <v>291</v>
       </c>
       <c r="H40" t="n">
         <v>291</v>
@@ -30623,7 +30623,7 @@
         <v>213</v>
       </c>
       <c r="L42" t="n">
-        <v>213</v>
+        <v>140.0914974254177</v>
       </c>
       <c r="M42" t="n">
         <v>213</v>
@@ -30635,7 +30635,7 @@
         <v>213</v>
       </c>
       <c r="P42" t="n">
-        <v>9.611785124016606</v>
+        <v>213</v>
       </c>
       <c r="Q42" t="n">
         <v>213</v>
@@ -30693,10 +30693,10 @@
         <v>213</v>
       </c>
       <c r="I43" t="n">
-        <v>213</v>
+        <v>176.6334556201183</v>
       </c>
       <c r="J43" t="n">
-        <v>213</v>
+        <v>97.69911798380934</v>
       </c>
       <c r="K43" t="n">
         <v>213</v>
@@ -30726,13 +30726,13 @@
         <v>213</v>
       </c>
       <c r="T43" t="n">
-        <v>213</v>
+        <v>210.0245665062577</v>
       </c>
       <c r="U43" t="n">
-        <v>213</v>
+        <v>150.9583912744579</v>
       </c>
       <c r="V43" t="n">
-        <v>213</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W43" t="n">
         <v>213</v>
@@ -30854,10 +30854,10 @@
         <v>187</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>187</v>
       </c>
       <c r="K45" t="n">
-        <v>187</v>
+        <v>19.01079029392637</v>
       </c>
       <c r="L45" t="n">
         <v>187</v>
@@ -30872,7 +30872,7 @@
         <v>187</v>
       </c>
       <c r="P45" t="n">
-        <v>161.0457473881675</v>
+        <v>187</v>
       </c>
       <c r="Q45" t="n">
         <v>187</v>
@@ -30933,7 +30933,7 @@
         <v>187</v>
       </c>
       <c r="J46" t="n">
-        <v>187</v>
+        <v>107.5617575331594</v>
       </c>
       <c r="K46" t="n">
         <v>187</v>
@@ -34746,7 +34746,7 @@
         <v>814</v>
       </c>
       <c r="K2" t="n">
-        <v>814.0000000000001</v>
+        <v>814</v>
       </c>
       <c r="L2" t="n">
         <v>814</v>
@@ -34880,31 +34880,31 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>154.95612715847</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>156.8412078007102</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>223.3665443798817</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>364.7310511640923</v>
       </c>
       <c r="K4" t="n">
-        <v>106.8031196030856</v>
+        <v>111.479226198857</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -34928,25 +34928,25 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>37.62652029714457</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>189.9754334937423</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>249.0416087255421</v>
       </c>
       <c r="V4" t="n">
         <v>200.8296897837838</v>
       </c>
       <c r="W4" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -34980,10 +34980,10 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>814.0000000000036</v>
+        <v>814</v>
       </c>
       <c r="K5" t="n">
-        <v>814.0000000000001</v>
+        <v>814</v>
       </c>
       <c r="L5" t="n">
         <v>814</v>
@@ -35117,31 +35117,31 @@
         <v>112.8861996629213</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D7" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>119.0190951630435</v>
       </c>
       <c r="F7" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>154.95612715847</v>
       </c>
       <c r="H7" t="n">
         <v>171.2288738983814</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>223.3665443798817</v>
       </c>
       <c r="J7" t="n">
-        <v>364.7310511640923</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>111.479226198857</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -35168,19 +35168,19 @@
         <v>37.62652029714457</v>
       </c>
       <c r="T7" t="n">
-        <v>189.9754334937423</v>
+        <v>15.75862254911732</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>249.0416087255421</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>108.1603073206878</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X7" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
@@ -35232,7 +35232,7 @@
         <v>814</v>
       </c>
       <c r="O8" t="n">
-        <v>814</v>
+        <v>814.0000000000045</v>
       </c>
       <c r="P8" t="n">
         <v>814</v>
@@ -35357,13 +35357,13 @@
         <v>127.2747533519553</v>
       </c>
       <c r="D10" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G10" t="n">
         <v>154.95612715847</v>
@@ -35372,10 +35372,10 @@
         <v>171.2288738983814</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>223.3665443798817</v>
       </c>
       <c r="J10" t="n">
-        <v>74.77588224525297</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>111.479226198857</v>
@@ -35405,19 +35405,19 @@
         <v>37.62652029714457</v>
       </c>
       <c r="T10" t="n">
-        <v>189.9754334937423</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>249.0416087255421</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>139.1830872424053</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X10" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -35454,28 +35454,28 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K11" t="n">
-        <v>161.6966466921584</v>
+        <v>716.8751175230993</v>
       </c>
       <c r="L11" t="n">
-        <v>814</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N11" t="n">
         <v>619.4144644189528</v>
       </c>
       <c r="O11" t="n">
-        <v>814</v>
+        <v>532.5214919778892</v>
       </c>
       <c r="P11" t="n">
-        <v>814</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35530,7 +35530,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>7.873614108651466</v>
       </c>
       <c r="J12" t="n">
         <v>350.2086062376757</v>
@@ -35539,13 +35539,13 @@
         <v>416.1038546407913</v>
       </c>
       <c r="L12" t="n">
-        <v>301.0818607161773</v>
+        <v>499.091375348687</v>
       </c>
       <c r="M12" t="n">
         <v>311.9500421645043</v>
       </c>
       <c r="N12" t="n">
-        <v>359.6265501086548</v>
+        <v>153.7434213674937</v>
       </c>
       <c r="O12" t="n">
         <v>466.4570219027464</v>
@@ -35703,13 +35703,13 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N14" t="n">
-        <v>362.2270756799963</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O14" t="n">
         <v>814</v>
       </c>
       <c r="P14" t="n">
-        <v>814</v>
+        <v>556.8126112610438</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -35767,25 +35767,25 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>33.87361410865147</v>
       </c>
       <c r="J15" t="n">
-        <v>376.2086062376757</v>
+        <v>125.2086062376757</v>
       </c>
       <c r="K15" t="n">
-        <v>191.1038546407913</v>
+        <v>442.1038546407913</v>
       </c>
       <c r="L15" t="n">
-        <v>525.0913753486871</v>
+        <v>274.091375348687</v>
       </c>
       <c r="M15" t="n">
-        <v>287.021947795233</v>
+        <v>86.95004216450428</v>
       </c>
       <c r="N15" t="n">
-        <v>134.6265501086548</v>
+        <v>300.8248416307324</v>
       </c>
       <c r="O15" t="n">
-        <v>241.4570219027464</v>
+        <v>492.4570219027464</v>
       </c>
       <c r="P15" t="n">
         <v>364.6660045146532</v>
@@ -35931,10 +35931,10 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K17" t="n">
-        <v>435.3966095009885</v>
+        <v>716.8751175230993</v>
       </c>
       <c r="L17" t="n">
-        <v>814</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>516.0089179080152</v>
@@ -35943,7 +35943,7 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>532.5214919778892</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -36010,7 +36010,7 @@
         <v>125.2086062376757</v>
       </c>
       <c r="K18" t="n">
-        <v>470.1038546407913</v>
+        <v>191.1038546407913</v>
       </c>
       <c r="L18" t="n">
         <v>274.091375348687</v>
@@ -36019,16 +36019,16 @@
         <v>86.95004216450428</v>
       </c>
       <c r="N18" t="n">
-        <v>413.6265501086548</v>
+        <v>134.6265501086548</v>
       </c>
       <c r="O18" t="n">
-        <v>285.9219611880214</v>
+        <v>459.001226278501</v>
       </c>
       <c r="P18" t="n">
-        <v>113.6660045146532</v>
+        <v>392.6660045146532</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>105.9207349095204</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -36168,16 +36168,16 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K20" t="n">
-        <v>716.8751175230993</v>
+        <v>240.811073919941</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="M20" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N20" t="n">
-        <v>337.9359563968417</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -36189,7 +36189,7 @@
         <v>443.0293889420883</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>5.512089101654111e-11</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -36408,25 +36408,25 @@
         <v>716.8751175230993</v>
       </c>
       <c r="L23" t="n">
-        <v>482.9742632469452</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O23" t="n">
-        <v>814</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>814</v>
+        <v>532.5214919778892</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R23" t="n">
-        <v>6.981979528761874e-11</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -36487,22 +36487,22 @@
         <v>191.1038546407913</v>
       </c>
       <c r="L24" t="n">
-        <v>274.091375348687</v>
+        <v>553.0913753486871</v>
       </c>
       <c r="M24" t="n">
-        <v>365.9500421645043</v>
+        <v>86.95004216450428</v>
       </c>
       <c r="N24" t="n">
-        <v>134.6265501086548</v>
+        <v>290.2971403757578</v>
       </c>
       <c r="O24" t="n">
-        <v>503.04834707937</v>
+        <v>241.4570219027464</v>
       </c>
       <c r="P24" t="n">
         <v>113.6660045146532</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>105.9207349095204</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -36639,13 +36639,13 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K26" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>772.9999999999999</v>
+        <v>676.4765574844688</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -36654,10 +36654,10 @@
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>773.0000000000275</v>
+        <v>773.0000000000266</v>
       </c>
       <c r="P26" t="n">
-        <v>354.8631703024613</v>
+        <v>773.0000000000266</v>
       </c>
       <c r="Q26" t="n">
         <v>443.0293889420883</v>
@@ -36727,13 +36727,13 @@
         <v>499.091375348687</v>
       </c>
       <c r="M27" t="n">
-        <v>106.0669134233433</v>
+        <v>311.9500421645043</v>
       </c>
       <c r="N27" t="n">
         <v>359.6265501086548</v>
       </c>
       <c r="O27" t="n">
-        <v>466.4570219027464</v>
+        <v>260.5738931615854</v>
       </c>
       <c r="P27" t="n">
         <v>338.6660045146532</v>
@@ -36888,16 +36888,16 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N29" t="n">
-        <v>216.5925220533724</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O29" t="n">
-        <v>773.0000000000348</v>
+        <v>773.0000000000339</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>40.20744657650906</v>
       </c>
       <c r="Q29" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -36967,13 +36967,13 @@
         <v>311.9500421645043</v>
       </c>
       <c r="N30" t="n">
-        <v>359.6265501086548</v>
+        <v>153.743421367494</v>
       </c>
       <c r="O30" t="n">
         <v>466.4570219027464</v>
       </c>
       <c r="P30" t="n">
-        <v>132.7828757734923</v>
+        <v>338.6660045146532</v>
       </c>
       <c r="Q30" t="n">
         <v>51.92073490952041</v>
@@ -37113,28 +37113,28 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>773.0000000000421</v>
+        <v>773.0000000000412</v>
       </c>
       <c r="K32" t="n">
-        <v>727.107932076301</v>
+        <v>727.1079320760724</v>
       </c>
       <c r="L32" t="n">
         <v>773</v>
       </c>
       <c r="M32" t="n">
-        <v>773.0000000000421</v>
+        <v>773.0000000000412</v>
       </c>
       <c r="N32" t="n">
-        <v>773.0000000000421</v>
+        <v>773.0000000000412</v>
       </c>
       <c r="O32" t="n">
-        <v>773.0000000000421</v>
+        <v>773.0000000000412</v>
       </c>
       <c r="P32" t="n">
-        <v>773.0000000000421</v>
+        <v>773.0000000000412</v>
       </c>
       <c r="Q32" t="n">
-        <v>773.0000000000421</v>
+        <v>773.0000000000412</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37192,19 +37192,19 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>253.0188164136765</v>
+        <v>125.2086062376757</v>
       </c>
       <c r="K33" t="n">
         <v>191.1038546407913</v>
       </c>
       <c r="L33" t="n">
-        <v>274.091375348687</v>
+        <v>565.0913753486871</v>
       </c>
       <c r="M33" t="n">
-        <v>377.9500421645043</v>
+        <v>86.95004216450428</v>
       </c>
       <c r="N33" t="n">
-        <v>134.6265501086548</v>
+        <v>144.5160253751351</v>
       </c>
       <c r="O33" t="n">
         <v>241.4570219027464</v>
@@ -37213,7 +37213,7 @@
         <v>113.6660045146532</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>117.9207349095204</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -37247,7 +37247,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3.886199662945266</v>
+        <v>3.886199662921342</v>
       </c>
       <c r="C34" t="n">
         <v>18.27475335195533</v>
@@ -37350,28 +37350,28 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>773.0000000000493</v>
+        <v>773.0000000000484</v>
       </c>
       <c r="K35" t="n">
-        <v>727.1079320763301</v>
+        <v>727.1079320760085</v>
       </c>
       <c r="L35" t="n">
-        <v>773.0000000000001</v>
+        <v>773</v>
       </c>
       <c r="M35" t="n">
-        <v>773.0000000000493</v>
+        <v>773.0000000000484</v>
       </c>
       <c r="N35" t="n">
-        <v>773.0000000000493</v>
+        <v>773.0000000000484</v>
       </c>
       <c r="O35" t="n">
-        <v>773.0000000000493</v>
+        <v>773.0000000000484</v>
       </c>
       <c r="P35" t="n">
-        <v>773.0000000000493</v>
+        <v>773.0000000000484</v>
       </c>
       <c r="Q35" t="n">
-        <v>773.0000000000493</v>
+        <v>773.0000000000484</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37426,16 +37426,16 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>73.87361410865147</v>
       </c>
       <c r="J36" t="n">
         <v>125.2086062376757</v>
       </c>
       <c r="K36" t="n">
-        <v>191.1038546407913</v>
+        <v>418.1197157986202</v>
       </c>
       <c r="L36" t="n">
-        <v>283.9808506151673</v>
+        <v>274.091375348687</v>
       </c>
       <c r="M36" t="n">
         <v>86.95004216450428</v>
@@ -37447,7 +37447,7 @@
         <v>241.4570219027464</v>
       </c>
       <c r="P36" t="n">
-        <v>404.6660045146532</v>
+        <v>113.6660045146532</v>
       </c>
       <c r="Q36" t="n">
         <v>117.9207349095204</v>
@@ -37484,7 +37484,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3.886199662945266</v>
+        <v>3.886199662921342</v>
       </c>
       <c r="C37" t="n">
         <v>18.27475335195533</v>
@@ -37587,28 +37587,28 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>773.0000000000566</v>
+        <v>773.0000000000557</v>
       </c>
       <c r="K38" t="n">
         <v>773</v>
       </c>
       <c r="L38" t="n">
-        <v>727.1079320762835</v>
+        <v>727.1079320759851</v>
       </c>
       <c r="M38" t="n">
-        <v>773.0000000000566</v>
+        <v>773.0000000000557</v>
       </c>
       <c r="N38" t="n">
-        <v>773.0000000000566</v>
+        <v>773.0000000000557</v>
       </c>
       <c r="O38" t="n">
-        <v>773.0000000000566</v>
+        <v>773.0000000000557</v>
       </c>
       <c r="P38" t="n">
-        <v>773.0000000000566</v>
+        <v>773.0000000000557</v>
       </c>
       <c r="Q38" t="n">
-        <v>773.0000000000566</v>
+        <v>773.0000000000557</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37681,13 +37681,13 @@
         <v>134.6265501086548</v>
       </c>
       <c r="O39" t="n">
-        <v>532.4570219027464</v>
+        <v>241.4570219027464</v>
       </c>
       <c r="P39" t="n">
-        <v>113.6660045146532</v>
+        <v>340.6818656724819</v>
       </c>
       <c r="Q39" t="n">
-        <v>53.93659606734907</v>
+        <v>117.9207349095204</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -37736,7 +37736,7 @@
         <v>16.61714403225807</v>
       </c>
       <c r="G40" t="n">
-        <v>45.95612715849753</v>
+        <v>45.95612715846997</v>
       </c>
       <c r="H40" t="n">
         <v>62.22887389838138</v>
@@ -37827,25 +37827,25 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K41" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>773</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>773.000000000063</v>
       </c>
       <c r="P41" t="n">
-        <v>732.6014399614226</v>
+        <v>757.0825640995796</v>
       </c>
       <c r="Q41" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37909,7 +37909,7 @@
         <v>404.1038546407913</v>
       </c>
       <c r="L42" t="n">
-        <v>487.091375348687</v>
+        <v>414.1828727741047</v>
       </c>
       <c r="M42" t="n">
         <v>299.9500421645043</v>
@@ -37921,7 +37921,7 @@
         <v>454.4570219027464</v>
       </c>
       <c r="P42" t="n">
-        <v>123.2777896386698</v>
+        <v>326.6660045146532</v>
       </c>
       <c r="Q42" t="n">
         <v>39.92073490952041</v>
@@ -37979,10 +37979,10 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>36.36654437988173</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>177.7310511640922</v>
+        <v>62.43016914790159</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -38012,13 +38012,13 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>2.975433493742287</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>62.04160872554206</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>13.82968978378381</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
         <v>0</v>
@@ -38064,22 +38064,22 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K44" t="n">
-        <v>57.06209306549079</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>773</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N44" t="n">
         <v>619.4144644189528</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>773.0000000000775</v>
       </c>
       <c r="P44" t="n">
-        <v>773.0000000000784</v>
+        <v>314.0531751574765</v>
       </c>
       <c r="Q44" t="n">
         <v>443.0293889420883</v>
@@ -38140,10 +38140,10 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>125.2086062376757</v>
+        <v>312.2086062376757</v>
       </c>
       <c r="K45" t="n">
-        <v>378.1038546407913</v>
+        <v>210.1146449347177</v>
       </c>
       <c r="L45" t="n">
         <v>461.091375348687</v>
@@ -38158,7 +38158,7 @@
         <v>428.4570219027464</v>
       </c>
       <c r="P45" t="n">
-        <v>274.7117519028208</v>
+        <v>300.6660045146532</v>
       </c>
       <c r="Q45" t="n">
         <v>13.92073490952041</v>
@@ -38219,7 +38219,7 @@
         <v>10.36654437988173</v>
       </c>
       <c r="J46" t="n">
-        <v>151.7310511640922</v>
+        <v>72.29280869725164</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
